--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.8€/kg)</t>
+          <t>€/m (6.75€/kg)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.5</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>7.37</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="7">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>11.47</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>16.52</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="9">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>29.48</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="10">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="11">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46.07</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="12">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>37.16</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>22.49</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="15">
@@ -1334,10 +1334,10 @@
         <v>335</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="16">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="17">
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="18">
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="19">
@@ -1543,13 +1543,13 @@
         <v>99</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="20">
@@ -1599,10 +1599,10 @@
         <v>4</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5.77</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="21">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>9.01</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="22">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>12.98</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="23">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>17.67</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="24">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>23.07</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="25">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>36.06</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="26">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>51.92</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="27">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="28">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>6.98</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="29">
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="30">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="31">
@@ -2186,10 +2186,10 @@
         <v>104</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="32">
@@ -2238,13 +2238,13 @@
         <v>329</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>800</v>
+        <v>748</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="33">
@@ -2293,13 +2293,13 @@
         <v>348</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>49</v>
+        <v>419</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>580</v>
+        <v>950</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="34">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="35">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>12</v>
@@ -2409,7 +2409,7 @@
         <v>185</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="36">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="37">
@@ -2516,10 +2516,10 @@
         <v>260</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>5.53</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="38">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>11.02</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="39">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="40">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>207</v>
@@ -2684,7 +2684,7 @@
         <v>18</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5.89</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="41">
@@ -2733,13 +2733,13 @@
         <v>144</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>7.37</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="42">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11.02</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="43">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="44">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="45">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="46">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="47">
@@ -3066,10 +3066,10 @@
         <v>201</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>7.34</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="48">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="49">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>73</v>
@@ -3179,7 +3179,7 @@
         <v>10</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>13.77</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="50">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>18.37</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="51">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>11.02</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="52">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>13.22</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="53">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>16.52</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="54">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>22.03</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="55">
@@ -3506,10 +3506,10 @@
         <v>78</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>12.85</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="56">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="57">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="58">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>14.74</v>
+        <v>14.63</v>
       </c>
     </row>
     <row r="59">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>22.11</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="60">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>29.38</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="61">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>14.69</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="62">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>18.42</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="63">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>21.61</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="64">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>21.99</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="65">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>26.44</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="66">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>35.8</v>
+        <v>35.54</v>
       </c>
     </row>
     <row r="67">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>27.53</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>9.18</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>20.65</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="70">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>36.72</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="71">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>14.69</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="72">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="73">
@@ -4493,13 +4493,13 @@
         <v>42</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>5.51</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="74">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="76">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="77">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="78">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="79">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="80">
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="81">
@@ -4933,13 +4933,13 @@
         <v>3</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="N81" s="5" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="82">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>36.72</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="83">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>33.05</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="84">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>44.06</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="85">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>55.08</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="86">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>27.02</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="87">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>8.81</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="88">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>41.31</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="89">
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>25.7</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="90">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>7.34</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="91">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="92">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>5.51</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="93">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.51</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="94">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>21.88</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="95">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>21.88</v>
+        <v>21.72</v>
       </c>
     </row>
     <row r="96">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>5.51</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="97">
@@ -5813,13 +5813,13 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N97" s="5" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="99">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="100">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="101">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="102">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>8.26</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>16.52</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="104">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>17.63</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="105">
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.41</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="106">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>13.22</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="107">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="108">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="109">
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="110">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>29.38</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="111">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="112">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>13.77</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="113">
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="114">
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="115">
@@ -6812,10 +6812,10 @@
         <v>66</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N115" s="5" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>11.28</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="116">
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>10.09</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="117">
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>16.48</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="118">
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>26.34</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="119">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>61.03</v>
+        <v>60.58</v>
       </c>
     </row>
     <row r="120">
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="121">
@@ -7154,10 +7154,10 @@
         <v>42</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N121" s="5" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>7.41</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="122">
@@ -7205,16 +7205,16 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>11</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N122" s="5" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="123">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="124">
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>23.57</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="125">
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>8.34</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="127">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="128">
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>8.23</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="129">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>6.26</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="130">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>16.3</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="131">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="132">
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="133">
@@ -7838,10 +7838,10 @@
         <v>34</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N133" s="5" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>10.42</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="134">
@@ -7906,7 +7906,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="135">
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="136">
@@ -8020,7 +8020,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="137">
@@ -8063,13 +8063,13 @@
         <v>62</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>234</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="138">
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="139">
@@ -8180,10 +8180,10 @@
         <v>258</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="140">
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="141">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="142">
@@ -8348,13 +8348,13 @@
         <v>122</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="143">
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>14.76</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="144">
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>22.32</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="145">
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>34.88</v>
+        <v>34.63</v>
       </c>
     </row>
     <row r="146">
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="147">
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="148">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="149">
@@ -8750,10 +8750,10 @@
         <v>375</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="N149" s="5" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>5.34</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="150">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -8861,13 +8861,13 @@
         <v>4</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N151" s="5" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="152">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>42.36</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="153">
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>42.36</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="154">
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>11.46</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="155">
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>21.37</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="156">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>10.85</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="157">
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>6.88</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="158">
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="159">
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>10.72</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="160">
@@ -9388,7 +9388,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="161">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="162">
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>10.98</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="163">
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>10.98</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="164">
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="165">
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>40.2</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="166">
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>44.21</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="167">
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="168">
@@ -9844,7 +9844,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>7.07</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="169">
@@ -9887,13 +9887,13 @@
         <v>138</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>8.51</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="171">
@@ -10001,13 +10001,13 @@
         <v>257</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>323</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>761</v>
+        <v>794</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="172">
@@ -10058,13 +10058,13 @@
         <v>109</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="173">
@@ -10129,7 +10129,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>15.86</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="174">
@@ -10175,10 +10175,10 @@
         <v>22</v>
       </c>
       <c r="L174" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>13.31</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="175">
@@ -10229,13 +10229,13 @@
         <v>71</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>383</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="176">
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="177">
@@ -10343,13 +10343,13 @@
         <v>0</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L177" s="2" t="n">
         <v>128</v>
       </c>
       <c r="M177" s="2" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N177" s="5" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="178">
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="180">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="181">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>6.41</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="182">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="183">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="184">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="185">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="186">
@@ -10870,7 +10870,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="187">
@@ -10927,7 +10927,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="188">
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="189">
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="190">
@@ -11098,7 +11098,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>10.3</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="191">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="192">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>6.35</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="193">
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="194">
@@ -11312,13 +11312,13 @@
         <v>188</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L194" s="2" t="n">
         <v>149</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N194" s="4" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="195">
@@ -11369,13 +11369,13 @@
         <v>204</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="196">
@@ -11440,7 +11440,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="197">
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="198">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="199">
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="200">
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>8.4</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="201">
@@ -11725,7 +11725,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="202">
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="203">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="204">
@@ -11896,7 +11896,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="205">
@@ -11939,13 +11939,13 @@
         <v>182</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>217</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="206">
@@ -11996,13 +11996,13 @@
         <v>40</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>7.21</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="207">
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>4.68</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="208">
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>124</v>
@@ -12116,7 +12116,7 @@
         <v>41</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N208" s="4" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="209">
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>10.09</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="210">
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>10.09</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="211">
@@ -12281,13 +12281,13 @@
         <v>45</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="N211" s="4" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="212">
@@ -12352,7 +12352,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>12.98</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="213">
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>12.98</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="214">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>12.97</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="215">
@@ -12523,7 +12523,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>15.86</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="216">
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>21.71</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="217">
@@ -12637,7 +12637,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>51.91</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="218">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>51.91</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="219">
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>26.32</v>
+        <v>26.12</v>
       </c>
     </row>
     <row r="220">
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>18.51</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="221">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>30.27</v>
+        <v>30.05</v>
       </c>
     </row>
     <row r="222">
@@ -12922,7 +12922,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>27.39</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="223">
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>27.39</v>
+        <v>27.19</v>
       </c>
     </row>
     <row r="224">
@@ -13036,7 +13036,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="225">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="226">
@@ -13139,10 +13139,10 @@
         <v>10</v>
       </c>
       <c r="L226" s="2" t="n">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="M226" s="2" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="N226" s="4" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="227">
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>13.37</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="228">
@@ -13264,7 +13264,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>24.51</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="229">
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>67.14</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="231">
@@ -13424,10 +13424,10 @@
         <v>31</v>
       </c>
       <c r="L231" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N231" s="4" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="232">
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>23.87</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="233">
@@ -13535,13 +13535,13 @@
         <v>1</v>
       </c>
       <c r="K233" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L233" s="2" t="n">
         <v>11</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N233" s="5" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>11.35</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="234">
@@ -13595,10 +13595,10 @@
         <v>161</v>
       </c>
       <c r="L234" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="N234" s="4" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>8.34</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>5.53</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="236">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>11.17</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="237">
@@ -13777,7 +13777,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="238">
@@ -13820,13 +13820,13 @@
         <v>282</v>
       </c>
       <c r="K238" s="2" t="n">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="L238" s="2" t="n">
         <v>590</v>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1604</v>
+        <v>1584</v>
       </c>
       <c r="N238" s="4" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="239">
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="240">
@@ -13948,7 +13948,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>20.25</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="241">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>8.77</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>5.55</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="244">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="245">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>71.09</v>
+        <v>70.56999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>15.22</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="247">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>42.7</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="248">
@@ -14404,7 +14404,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="249">
@@ -14461,7 +14461,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="250">
@@ -14518,7 +14518,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>7.81</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="251">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>6.11</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="252">
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="253">
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>22.22</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="254">
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="255">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="J255" s="2" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K255" s="2" t="n">
         <v>241</v>
@@ -14795,7 +14795,7 @@
         <v>137</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="256">
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="257">
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="258">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="259">
@@ -15031,7 +15031,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="260">
@@ -15074,13 +15074,13 @@
         <v>29</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L260" s="2" t="n">
         <v>58</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="261">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>6.92</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="262">
@@ -15202,7 +15202,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>10.57</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="263">
@@ -15259,7 +15259,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="264">
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K264" s="2" t="n">
         <v>162</v>
@@ -15308,7 +15308,7 @@
         <v>49</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>13.51</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="265">
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>12.61</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="266">
@@ -15416,13 +15416,13 @@
         <v>28</v>
       </c>
       <c r="K266" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L266" s="2" t="n">
         <v>41</v>
       </c>
       <c r="M266" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N266" s="4" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>16.45</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="267">
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>16.45</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="268">
@@ -15544,7 +15544,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>19.38</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="269">
@@ -15601,7 +15601,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>22.32</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="270">
@@ -15658,7 +15658,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>42.3</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="271">
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>28.1</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="272">
@@ -15772,7 +15772,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>17.03</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="273">
@@ -15812,16 +15812,16 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L273" s="2" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M273" s="2" t="n">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="N273" s="4" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="274">
@@ -15886,7 +15886,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>6.32</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="275">
@@ -15943,7 +15943,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -16000,7 +16000,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="277">
@@ -16057,7 +16057,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>27.16</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="278">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>27.16</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="279">
@@ -16171,7 +16171,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>42.23</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="280">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="281">
@@ -16285,7 +16285,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -16388,10 +16388,10 @@
         <v>328</v>
       </c>
       <c r="L283" s="2" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="M283" s="2" t="n">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="N283" s="4" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>8.15</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="284">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="285">
@@ -16513,7 +16513,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>10.32</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="286">
@@ -16570,7 +16570,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>5.81</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="287">
@@ -16627,7 +16627,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>12.55</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="288">
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>13.37</v>
+        <v>13.27</v>
       </c>
     </row>
     <row r="289">
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>41.04</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="290">
@@ -16798,7 +16798,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>10.36</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="291">
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>28.12</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="292">
@@ -16912,7 +16912,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>28.12</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="293">
@@ -16952,7 +16952,7 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K293" s="2" t="n">
         <v>342</v>
@@ -16961,7 +16961,7 @@
         <v>105</v>
       </c>
       <c r="M293" s="2" t="n">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="N293" s="4" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="294">
@@ -17026,7 +17026,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="295">
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>21.82</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="296">
@@ -17140,7 +17140,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>71.13</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="297">
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>71.13</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="298">
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>71.13</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="299">
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>10.56</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="300">
@@ -17351,16 +17351,16 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K300" s="2" t="n">
         <v>89</v>
       </c>
       <c r="L300" s="2" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="M300" s="2" t="n">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="N300" s="4" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="301">
@@ -17425,7 +17425,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="302">
@@ -17465,16 +17465,16 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="L302" s="2" t="n">
         <v>70</v>
       </c>
       <c r="M302" s="2" t="n">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="N302" s="4" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="303">
@@ -17528,10 +17528,10 @@
         <v>170</v>
       </c>
       <c r="L303" s="2" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>8.15</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="304">
@@ -17579,13 +17579,13 @@
         </is>
       </c>
       <c r="J304" s="2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K304" s="2" t="n">
         <v>4</v>
       </c>
       <c r="L304" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M304" s="2" t="n">
         <v>41</v>
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="305">
@@ -17642,10 +17642,10 @@
         <v>109</v>
       </c>
       <c r="L305" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M305" s="2" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="N305" s="4" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>10.36</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="306">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>10.36</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="307">
@@ -17767,7 +17767,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>10.39</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="308">
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="J308" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K308" s="2" t="n">
         <v>156</v>
@@ -17816,7 +17816,7 @@
         <v>66</v>
       </c>
       <c r="M308" s="2" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>16.45</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="309">
@@ -17867,13 +17867,13 @@
         <v>42</v>
       </c>
       <c r="K309" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L309" s="2" t="n">
         <v>18</v>
       </c>
       <c r="M309" s="2" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>19.39</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="310">
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>20.86</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="311">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="312">
@@ -18052,7 +18052,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="313">
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>41.67</v>
+        <v>41.36</v>
       </c>
     </row>
     <row r="314">
@@ -18152,13 +18152,13 @@
         <v>0</v>
       </c>
       <c r="K314" s="2" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L314" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M314" s="2" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="N314" s="5" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>23.35</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="315">
@@ -18223,7 +18223,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>24.68</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="316">
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>9.25</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="317">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>18.07</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="318">
@@ -18394,7 +18394,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>9.99</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="319">
@@ -18451,7 +18451,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>19.39</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="320">
@@ -18494,13 +18494,13 @@
         <v>115</v>
       </c>
       <c r="K320" s="2" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L320" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M320" s="2" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="N320" s="4" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -18622,7 +18622,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="324">
@@ -18719,7 +18719,7 @@
         </is>
       </c>
       <c r="J324" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K324" s="2" t="n">
         <v>142</v>
@@ -18728,15 +18728,15 @@
         <v>15</v>
       </c>
       <c r="M324" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="N324" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>157</v>
+      </c>
+      <c r="N324" s="5" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>10.72</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="325">
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="J325" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K325" s="2" t="n">
         <v>19</v>
@@ -18785,15 +18785,15 @@
         <v>0</v>
       </c>
       <c r="M325" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="N325" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>19</v>
+      </c>
+      <c r="N325" s="5" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>10.72</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="326">
@@ -18850,7 +18850,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>21.35</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="327">
@@ -18907,7 +18907,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>16.16</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="328">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>14.43</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="329">
@@ -19004,24 +19004,24 @@
         </is>
       </c>
       <c r="J329" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K329" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L329" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M329" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="N329" s="5" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>52</v>
+      </c>
+      <c r="N329" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>12.93</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="330">
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>25.26</v>
+        <v>25.08</v>
       </c>
     </row>
     <row r="331">
@@ -19135,7 +19135,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="332">
@@ -19178,13 +19178,13 @@
         <v>7</v>
       </c>
       <c r="K332" s="2" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L332" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M332" s="2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N332" s="5" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>21.32</v>
+        <v>21.16</v>
       </c>
     </row>
     <row r="333">
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="334">
@@ -19289,7 +19289,7 @@
         </is>
       </c>
       <c r="J334" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K334" s="2" t="n">
         <v>87</v>
@@ -19298,7 +19298,7 @@
         <v>9</v>
       </c>
       <c r="M334" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N334" s="4" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>16.96</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="335">
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>25.78</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="336">
@@ -19406,13 +19406,13 @@
         <v>92</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L336" s="2" t="n">
         <v>51</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="N336" s="4" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>12.59</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="337">
@@ -19477,7 +19477,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>7.09</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="338">
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>7.09</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="339">
@@ -19591,7 +19591,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>7.62</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="340">
@@ -19648,7 +19648,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>7.81</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="341">
@@ -19705,7 +19705,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>7.81</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="342">
@@ -19762,7 +19762,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="343">
@@ -19819,7 +19819,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="344">
@@ -19865,10 +19865,10 @@
         <v>286</v>
       </c>
       <c r="L344" s="2" t="n">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="345">
@@ -19933,7 +19933,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>5.22</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="346">
@@ -19990,7 +19990,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>48.84</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="347">
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="348">
@@ -20104,7 +20104,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349">
@@ -20161,7 +20161,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="350">
@@ -20218,7 +20218,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="351">
@@ -20275,7 +20275,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="352">
@@ -20332,7 +20332,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="353">
@@ -20389,7 +20389,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>12.56</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="354">
@@ -20446,7 +20446,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>20.52</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="355">
@@ -20492,10 +20492,10 @@
         <v>1</v>
       </c>
       <c r="L355" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M355" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N355" s="4" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>20.93</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="356">
@@ -20560,7 +20560,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>41.43</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="357">
@@ -20617,7 +20617,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>9.25</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="358">
@@ -20674,7 +20674,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>13.33</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="359">
@@ -20731,7 +20731,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>13.33</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="360">
@@ -20788,7 +20788,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>34.92</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="361">
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>34.92</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="362">
@@ -20902,7 +20902,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>34.92</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="363">
@@ -20959,7 +20959,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>34.92</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="364">
@@ -21016,7 +21016,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>34.92</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="365">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>17.92</v>
+        <v>17.79</v>
       </c>
     </row>
     <row r="366">
@@ -21119,10 +21119,10 @@
         <v>2</v>
       </c>
       <c r="L366" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M366" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N366" s="5" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>34.61</v>
+        <v>34.36</v>
       </c>
     </row>
     <row r="367">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>14.4</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="368">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>9.99</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="369">
@@ -21301,7 +21301,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="370">
@@ -21358,7 +21358,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>13.51</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="371">
@@ -21415,7 +21415,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>5.61</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="372">
@@ -21472,7 +21472,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>28.22</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="373">
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>17.91</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="374">
@@ -21586,7 +21586,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>17.91</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="375">
@@ -21643,7 +21643,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>23.81</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="376">
@@ -21700,7 +21700,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>13.67</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="377">
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>12.93</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="378">
@@ -21814,7 +21814,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="379">
@@ -21871,7 +21871,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>6.32</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="380">
@@ -21928,7 +21928,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>7.79</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="381">
@@ -21985,7 +21985,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>14.4</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="382">
@@ -22042,7 +22042,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>14.98</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="383">
@@ -22099,7 +22099,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="384">
@@ -22156,7 +22156,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>9.25</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="385">
@@ -22213,7 +22213,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>16.99</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="386">
@@ -22270,7 +22270,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>13.67</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="387">
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="388">
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>34.28</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="389">
@@ -22441,7 +22441,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="390">
@@ -22498,7 +22498,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>15.87</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="391">
@@ -22555,7 +22555,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>18.82</v>
+        <v>18.68</v>
       </c>
     </row>
     <row r="392">
@@ -22612,7 +22612,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>28.2</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="393">
@@ -22669,7 +22669,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="394">
@@ -22726,7 +22726,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="395">
@@ -22783,7 +22783,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="396">
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>6.19</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="397">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="398">
@@ -22950,7 +22950,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="399">
@@ -23005,7 +23005,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="400">
@@ -23060,7 +23060,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="401">
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="402">
@@ -23155,7 +23155,7 @@
         </is>
       </c>
       <c r="J402" s="2" t="n">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="K402" s="2" t="n">
         <v>0</v>
@@ -23164,7 +23164,7 @@
         <v>0</v>
       </c>
       <c r="M402" s="2" t="n">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="403">
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="404">
@@ -23272,13 +23272,13 @@
         <v>0</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>60</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="N404" s="5" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="405">
@@ -23343,7 +23343,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="406">
@@ -23386,13 +23386,13 @@
         <v>80</v>
       </c>
       <c r="K406" s="2" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L406" s="2" t="n">
         <v>168</v>
       </c>
       <c r="M406" s="2" t="n">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N406" s="4" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="407">
@@ -23446,10 +23446,10 @@
         <v>682</v>
       </c>
       <c r="L407" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M407" s="2" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="408">
@@ -23571,7 +23571,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="410">
@@ -23628,7 +23628,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="411">
@@ -23685,7 +23685,7 @@
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="412">
@@ -23742,7 +23742,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="413">
@@ -23785,13 +23785,13 @@
         <v>245</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>1921</v>
+        <v>1911</v>
       </c>
       <c r="L413" s="2" t="n">
         <v>665</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2831</v>
+        <v>2821</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="J414" s="2" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="K414" s="2" t="n">
         <v>667</v>
@@ -23848,7 +23848,7 @@
         <v>91</v>
       </c>
       <c r="M414" s="2" t="n">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="N414" s="4" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="415">
@@ -23913,7 +23913,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="416">
@@ -23970,7 +23970,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="417">
@@ -24027,7 +24027,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="418">
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="419">
@@ -24124,16 +24124,16 @@
         </is>
       </c>
       <c r="J419" s="2" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L419" s="2" t="n">
         <v>256</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="420">
@@ -24198,7 +24198,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="421">
@@ -24255,7 +24255,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="422">
@@ -24312,7 +24312,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="423">
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="424">
@@ -24412,13 +24412,13 @@
         <v>85</v>
       </c>
       <c r="K424" s="2" t="n">
-        <v>167</v>
+        <v>642</v>
       </c>
       <c r="L424" s="2" t="n">
         <v>131</v>
       </c>
       <c r="M424" s="2" t="n">
-        <v>383</v>
+        <v>858</v>
       </c>
       <c r="N424" s="4" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="425">
@@ -24483,7 +24483,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="426">
@@ -24540,7 +24540,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="427">
@@ -24597,7 +24597,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="428">
@@ -24654,7 +24654,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="429">
@@ -24711,7 +24711,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="430">
@@ -24768,7 +24768,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="431">
@@ -24825,7 +24825,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="432">
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="433">
@@ -24928,10 +24928,10 @@
         <v>35</v>
       </c>
       <c r="L433" s="2" t="n">
-        <v>35</v>
+        <v>305</v>
       </c>
       <c r="M433" s="2" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="N433" s="4" t="inlineStr">
         <is>
@@ -24939,7 +24939,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="434">
@@ -24996,7 +24996,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="435">
@@ -25053,7 +25053,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="436">
@@ -25110,7 +25110,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="437">
@@ -25167,7 +25167,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="438">
@@ -25224,7 +25224,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="439">
@@ -25264,16 +25264,16 @@
         </is>
       </c>
       <c r="J439" s="2" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K439" s="2" t="n">
         <v>219</v>
       </c>
       <c r="L439" s="2" t="n">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="M439" s="2" t="n">
-        <v>437</v>
+        <v>709</v>
       </c>
       <c r="N439" s="4" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="440">
@@ -25321,16 +25321,16 @@
         </is>
       </c>
       <c r="J440" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K440" s="2" t="n">
         <v>225</v>
       </c>
       <c r="L440" s="2" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="N440" s="5" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="441">
@@ -25381,13 +25381,13 @@
         <v>167</v>
       </c>
       <c r="K441" s="2" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L441" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M441" s="2" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N441" s="4" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="442">
@@ -25452,7 +25452,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="443">
@@ -25498,10 +25498,10 @@
         <v>112</v>
       </c>
       <c r="L443" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M443" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N443" s="5" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="444">
@@ -25566,7 +25566,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="445">
@@ -25623,7 +25623,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="446">
@@ -25666,13 +25666,13 @@
         <v>5</v>
       </c>
       <c r="K446" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L446" s="2" t="n">
         <v>94</v>
       </c>
       <c r="M446" s="2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N446" s="5" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="447">
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>6.56</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="448">
@@ -25794,7 +25794,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>8.65</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="449">
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="450">
@@ -25908,7 +25908,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="451">
@@ -25965,7 +25965,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="452">
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>17.33</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="453">
@@ -26079,7 +26079,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="454">
@@ -26122,13 +26122,13 @@
         <v>356</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>925</v>
+        <v>898</v>
       </c>
       <c r="N454" s="4" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="455">
@@ -26179,13 +26179,13 @@
         <v>275</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>213</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="456">
@@ -26236,13 +26236,13 @@
         <v>42</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L456" s="2" t="n">
         <v>209</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="N456" s="4" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="457">
@@ -26307,7 +26307,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="458">
@@ -26350,13 +26350,13 @@
         <v>26</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="N458" s="4" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="459">
@@ -26421,7 +26421,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="460">
@@ -26464,13 +26464,13 @@
         <v>53</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N460" s="4" t="inlineStr">
         <is>
@@ -26478,7 +26478,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="461">
@@ -26521,13 +26521,13 @@
         <v>1</v>
       </c>
       <c r="K461" s="2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L461" s="2" t="n">
         <v>111</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N461" s="5" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="462">
@@ -26592,7 +26592,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>7.55</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="463">
@@ -26649,7 +26649,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>7.55</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="464">
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>10.39</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="465">
@@ -26763,7 +26763,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>10.91</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="466">
@@ -26806,13 +26806,13 @@
         <v>11</v>
       </c>
       <c r="K466" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L466" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M466" s="2" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N466" s="4" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="467">
@@ -26877,7 +26877,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="468">
@@ -26917,16 +26917,16 @@
         </is>
       </c>
       <c r="J468" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K468" s="2" t="n">
         <v>82</v>
       </c>
       <c r="L468" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M468" s="2" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="469">
@@ -26991,7 +26991,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="470">
@@ -27034,13 +27034,13 @@
         <v>11</v>
       </c>
       <c r="K470" s="2" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="L470" s="2" t="n">
         <v>93</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="N470" s="4" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>6.47</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="471">
@@ -27091,13 +27091,13 @@
         <v>19</v>
       </c>
       <c r="K471" s="2" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="L471" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M471" s="2" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N471" s="4" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>7.58</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="472">
@@ -27162,7 +27162,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="473">
@@ -27219,7 +27219,7 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>8.65</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="474">
@@ -27259,7 +27259,7 @@
         </is>
       </c>
       <c r="J474" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K474" s="2" t="n">
         <v>0</v>
@@ -27268,7 +27268,7 @@
         <v>0</v>
       </c>
       <c r="M474" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N474" s="4" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>8.65</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="475">
@@ -27319,13 +27319,13 @@
         <v>1</v>
       </c>
       <c r="K475" s="2" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L475" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M475" s="2" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="N475" s="5" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="476">
@@ -27390,7 +27390,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="477">
@@ -27447,7 +27447,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="478">
@@ -27504,7 +27504,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>10.38</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="479">
@@ -27561,7 +27561,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="480">
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="481">
@@ -27675,7 +27675,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="482">
@@ -27732,7 +27732,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="483">
@@ -27789,7 +27789,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="484">
@@ -27846,7 +27846,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="485">
@@ -27903,7 +27903,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="486">
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="487">
@@ -28017,7 +28017,7 @@
         </is>
       </c>
       <c r="O487" s="2" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="488">
@@ -28074,7 +28074,7 @@
         </is>
       </c>
       <c r="O488" s="2" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="489">
@@ -28131,7 +28131,7 @@
         </is>
       </c>
       <c r="O489" s="2" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="490">
@@ -28188,7 +28188,7 @@
         </is>
       </c>
       <c r="O490" s="2" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="491">
@@ -28245,7 +28245,7 @@
         </is>
       </c>
       <c r="O491" s="2" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="492">
@@ -28288,13 +28288,13 @@
         <v>7</v>
       </c>
       <c r="K492" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L492" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M492" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N492" s="5" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="O492" s="2" t="n">
-        <v>5.93</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="493">
@@ -28359,7 +28359,7 @@
         </is>
       </c>
       <c r="O493" s="2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="494">
@@ -28416,7 +28416,7 @@
         </is>
       </c>
       <c r="O494" s="2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.75€/kg)</t>
+          <t>€/m (6.65€/kg)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.41</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>82.01000000000001</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="7">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.32</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="8">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>17</v>
@@ -956,7 +956,7 @@
         <v>14</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>11.39</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="9">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.4</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="10">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>29.27</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="11">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="12">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>45.73</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>36.89</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="14">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>22.33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="16">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="17">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="18">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>116</v>
@@ -1604,7 +1604,7 @@
         <v>86</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="21">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>4</v>
@@ -1657,7 +1657,7 @@
         <v>84</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>5.72</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="22">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>8.94</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="23">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>12.89</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="24">
@@ -1810,13 +1810,13 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>17.54</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="25">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>22.9</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="26">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>35.8</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="27">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>51.54</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="28">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="29">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>6.93</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="30">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="31">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="32">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="33">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="34">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="35">
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>162</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="37">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="38">
@@ -2568,13 +2568,13 @@
         <v>80</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>5.49</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="39">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>10.94</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="40">
@@ -2678,13 +2678,13 @@
         <v>63</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>494</v>
+        <v>607</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>174</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>731</v>
+        <v>844</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="41">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>5.85</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="42">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>7.32</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="43">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>10.94</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="44">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="46">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="47">
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="48">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>7.29</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="49">
@@ -3173,13 +3173,13 @@
         <v>21</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>62</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>9.15</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="50">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>13.67</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="51">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>18.23</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="52">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>10.94</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="53">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>13.12</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="54">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>16.4</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="55">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>21.86</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="56">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>12.75</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="57">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.7</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="58">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>11.7</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="59">
@@ -3720,16 +3720,16 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>21</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>14.63</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="60">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>21.95</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="61">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>29.16</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="62">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>14.58</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="63">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>18.29</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="64">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>21.45</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="65">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>21.83</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="66">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>26.24</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="67">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>35.54</v>
+        <v>35.01</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>27.32</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="69">
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>9.109999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="70">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="71">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>36.45</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="72">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>14.58</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="73">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="74">
@@ -4548,13 +4548,13 @@
         <v>42</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="75">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="76">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="78">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="79">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="80">
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="81">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="82">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="83">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>36.45</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="84">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>32.8</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="85">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>43.74</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="86">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>54.68</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="87">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>26.82</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="88">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>41.01</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="90">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>25.51</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="91">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>32</v>
@@ -5489,7 +5489,7 @@
         <v>21</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>7.29</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="92">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="93">
@@ -5593,13 +5593,13 @@
         <v>216</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>103</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="94">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="95">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>21.72</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="96">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>21.72</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="97">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="98">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="99">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="100">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="101">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="102">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="103">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="104">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>16.4</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="105">
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>17.5</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="106">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="107">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>13.12</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="108">
@@ -6421,10 +6421,10 @@
         <v>79</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="109">
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="110">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="111">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>29.16</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="112">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="113">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>13.67</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="114">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="115">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="116">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>11.2</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="117">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>10.02</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -6978,13 +6978,13 @@
         <v>27</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>16.36</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="119">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>26.14</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="120">
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>60.58</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="121">
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>52</v>
@@ -7155,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="122">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="123">
@@ -7263,13 +7263,13 @@
         <v>7</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="124">
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="125">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>23.4</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="126">
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="127">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>8.44</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="128">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>8.44</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="129">
@@ -7605,13 +7605,13 @@
         <v>64</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>8.17</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>6.21</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="131">
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>16.18</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="132">
@@ -7779,10 +7779,10 @@
         <v>208</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="133">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>58</v>
@@ -7839,7 +7839,7 @@
         <v>75</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>8.24</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>10.35</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="135">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="136">
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="137">
@@ -8061,13 +8061,13 @@
         <v>28</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>3.11</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="138">
@@ -8118,13 +8118,13 @@
         <v>62</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>234</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="139">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="140">
@@ -8232,13 +8232,13 @@
         <v>47</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="141">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>8.66</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>29</v>
@@ -8352,7 +8352,7 @@
         <v>2</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>8.66</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="144">
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>14.65</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="145">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>22.16</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="146">
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>34.63</v>
+        <v>34.11</v>
       </c>
     </row>
     <row r="147">
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="K147" s="2" t="n">
         <v>381</v>
@@ -8637,7 +8637,7 @@
         <v>238</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="148">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="149">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="150">
@@ -8802,13 +8802,13 @@
         <v>0</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>18</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>5.31</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="151">
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K151" s="2" t="n">
         <v>43</v>
@@ -8865,7 +8865,7 @@
         <v>73</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="152">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>5.92</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="153">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>42.05</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="154">
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>42.05</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="155">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>11.37</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="156">
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>21.22</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="157">
@@ -9204,10 +9204,10 @@
         <v>0</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>10.77</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="158">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>6.83</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="159">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="160">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>10.64</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="161">
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="162">
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="163">
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>10.89</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="164">
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>10.89</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="165">
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="166">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>39.91</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="167">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>43.89</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="168">
@@ -9831,10 +9831,10 @@
         <v>596</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1095</v>
+        <v>1080</v>
       </c>
       <c r="N168" s="4" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="169">
@@ -9888,10 +9888,10 @@
         <v>139</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>7.02</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="170">
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="171">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="172">
@@ -10056,13 +10056,13 @@
         <v>256</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="173">
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>4.21</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="174">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>15.75</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="175">
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>13.22</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="176">
@@ -10284,13 +10284,13 @@
         <v>71</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="L176" s="2" t="n">
         <v>380</v>
       </c>
       <c r="M176" s="2" t="n">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="177">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="178">
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="179">
@@ -10455,13 +10455,13 @@
         <v>0</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="L179" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M179" s="2" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="181">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.08</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="182">
@@ -10640,7 +10640,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>6.36</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="183">
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="184">
@@ -10754,7 +10754,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="185">
@@ -10797,13 +10797,13 @@
         <v>0</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>302</v>
+        <v>134</v>
       </c>
       <c r="L185" s="2" t="n">
         <v>100</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>402</v>
+        <v>234</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="186">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="187">
@@ -10911,13 +10911,13 @@
         <v>0</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M187" s="2" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="188">
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="189">
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="190">
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="191">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>10.23</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="192">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="193">
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>6.31</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="194">
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="195">
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K195" s="2" t="n">
         <v>131</v>
@@ -11373,7 +11373,7 @@
         <v>149</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="196">
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="197">
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="198">
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>8.65</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -11609,7 +11609,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="200">
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="201">
@@ -11723,7 +11723,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>8.34</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -11763,16 +11763,16 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L202" s="2" t="n">
         <v>299</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="203">
@@ -11820,16 +11820,16 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>78</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="204">
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="205">
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>5.48</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="206">
@@ -11994,13 +11994,13 @@
         <v>182</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>217</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="207">
@@ -12051,13 +12051,13 @@
         <v>40</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>7.16</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="208">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="209">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="210">
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>10.02</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -12276,16 +12276,16 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>89</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N211" s="6" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>10.02</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -12336,13 +12336,13 @@
         <v>45</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>8.07</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="213">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>12.88</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="214">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>12.88</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="215">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>12.87</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="216">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>15.74</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="217">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>21.55</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="218">
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>51.53</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="219">
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>51.53</v>
+        <v>50.77</v>
       </c>
     </row>
     <row r="220">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>26.12</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="221">
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>18.37</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="222">
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>30.05</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="223">
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>27.19</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="224">
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>27.19</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="225">
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="226">
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="227">
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>13.27</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="229">
@@ -13319,7 +13319,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>24.33</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="230">
@@ -13376,7 +13376,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>66.65000000000001</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="231">
@@ -13419,13 +13419,13 @@
         <v>396</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="L231" s="2" t="n">
         <v>691</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1423</v>
+        <v>1414</v>
       </c>
       <c r="N231" s="4" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="232">
@@ -13476,13 +13476,13 @@
         <v>16</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="N232" s="4" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>6.64</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="233">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>23.69</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="234">
@@ -13604,7 +13604,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>11.27</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="235">
@@ -13650,10 +13650,10 @@
         <v>102</v>
       </c>
       <c r="L235" s="2" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M235" s="2" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="N235" s="4" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>8.279999999999999</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="236">
@@ -13701,16 +13701,16 @@
         </is>
       </c>
       <c r="J236" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K236" s="2" t="n">
         <v>12</v>
       </c>
       <c r="L236" s="2" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="N236" s="4" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>5.49</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="237">
@@ -13775,7 +13775,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="238">
@@ -13832,7 +13832,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>8.23</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="239">
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="240">
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="241">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="242">
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="243">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="244">
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>5.51</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="245">
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="246">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>70.56999999999999</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="247">
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>15.11</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="248">
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>42.39</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="249">
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="250">
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="251">
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>7.75</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="252">
@@ -14616,13 +14616,13 @@
         <v>18</v>
       </c>
       <c r="K252" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L252" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M252" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N252" s="4" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>6.07</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="253">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="254">
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>22.06</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="255">
@@ -14790,10 +14790,10 @@
         <v>0</v>
       </c>
       <c r="L255" s="2" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="256">
@@ -14858,7 +14858,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="257">
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="258">
@@ -14972,7 +14972,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="259">
@@ -15012,16 +15012,16 @@
         </is>
       </c>
       <c r="J259" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L259" s="2" t="n">
         <v>190</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="260">
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="261">
@@ -15129,13 +15129,13 @@
         <v>29</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="L261" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="262">
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>6.86</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="263">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>10.49</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="264">
@@ -15300,13 +15300,13 @@
         <v>94</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L264" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="265">
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>13.41</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="266">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>12.52</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="267">
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>16.33</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="268">
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>16.33</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="269">
@@ -15599,7 +15599,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>19.24</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="270">
@@ -15642,13 +15642,13 @@
         <v>55</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L270" s="2" t="n">
         <v>74</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>22.15</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="271">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>41.99</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="272">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K272" s="2" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
         <v>40</v>
       </c>
       <c r="M272" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>27.89</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="273">
@@ -15813,13 +15813,13 @@
         <v>39</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L273" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M273" s="2" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N273" s="4" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>16.91</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="274">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="275">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>6.28</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="276">
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>26.96</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="279">
@@ -16169,7 +16169,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>26.96</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="280">
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>41.92</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="281">
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>5.05</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="282">
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="283">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="284">
@@ -16454,7 +16454,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>8.09</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="285">
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="286">
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>10.25</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="287">
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>5.76</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="288">
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>12.45</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="289">
@@ -16739,7 +16739,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>13.27</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="290">
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>40.74</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="291">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>10.28</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="292">
@@ -16910,7 +16910,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>27.92</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="293">
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>27.92</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="294">
@@ -17024,7 +17024,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="295">
@@ -17081,7 +17081,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="296">
@@ -17138,7 +17138,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>21.66</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="297">
@@ -17195,7 +17195,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>70.61</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="298">
@@ -17252,7 +17252,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>70.61</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="299">
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>70.61</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>10.48</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="301">
@@ -17409,13 +17409,13 @@
         <v>50</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="L301" s="2" t="n">
         <v>77</v>
       </c>
       <c r="M301" s="2" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>4.08</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="302">
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>4.08</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="303">
@@ -17537,7 +17537,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="304">
@@ -17580,13 +17580,13 @@
         <v>130</v>
       </c>
       <c r="K304" s="2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L304" s="2" t="n">
-        <v>18</v>
+        <v>140</v>
       </c>
       <c r="M304" s="2" t="n">
-        <v>318</v>
+        <v>439</v>
       </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>8.09</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="305">
@@ -17637,13 +17637,13 @@
         <v>0</v>
       </c>
       <c r="K305" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L305" s="2" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="M305" s="2" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="N305" s="6" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>5.54</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="306">
@@ -17694,13 +17694,13 @@
         <v>54</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="L306" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>10.28</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="307">
@@ -17765,7 +17765,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>10.28</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="308">
@@ -17808,13 +17808,13 @@
         <v>81</v>
       </c>
       <c r="K308" s="2" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L308" s="2" t="n">
         <v>60</v>
       </c>
       <c r="M308" s="2" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>10.31</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="309">
@@ -17865,13 +17865,13 @@
         <v>38</v>
       </c>
       <c r="K309" s="2" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L309" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M309" s="2" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>16.32</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="310">
@@ -17922,13 +17922,13 @@
         <v>42</v>
       </c>
       <c r="K310" s="2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L310" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M310" s="2" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>19.25</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="311">
@@ -17979,13 +17979,13 @@
         <v>12</v>
       </c>
       <c r="K311" s="2" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L311" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M311" s="2" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="N311" s="4" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="312">
@@ -18036,13 +18036,13 @@
         <v>169</v>
       </c>
       <c r="K312" s="2" t="n">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="L312" s="2" t="n">
         <v>90</v>
       </c>
       <c r="M312" s="2" t="n">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="N312" s="4" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="313">
@@ -18107,7 +18107,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="314">
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>41.36</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="315">
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>23.18</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="316">
@@ -18264,13 +18264,13 @@
         <v>24</v>
       </c>
       <c r="K316" s="2" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="L316" s="2" t="n">
         <v>13</v>
       </c>
       <c r="M316" s="2" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="N316" s="4" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>24.5</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="317">
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>9.18</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="318">
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>17.93</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="319">
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>9.92</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="320">
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>19.24</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="321">
@@ -18563,7 +18563,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>30.98</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="322">
@@ -18620,7 +18620,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="323">
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="324">
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="325">
@@ -18791,7 +18791,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="326">
@@ -18834,13 +18834,13 @@
         <v>44</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L326" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M326" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>10.64</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="327">
@@ -18905,7 +18905,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>10.64</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="328">
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>21.2</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="329">
@@ -19019,7 +19019,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>16.04</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="330">
@@ -19076,7 +19076,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>14.32</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="331">
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>12.83</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="332">
@@ -19173,7 +19173,7 @@
         </is>
       </c>
       <c r="J332" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K332" s="2" t="n">
         <v>5</v>
@@ -19182,7 +19182,7 @@
         <v>0</v>
       </c>
       <c r="M332" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>25.08</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="333">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="334">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>21.16</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="335">
@@ -19350,10 +19350,10 @@
         <v>76</v>
       </c>
       <c r="L335" s="2" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="336">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>16.84</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="337">
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>25.59</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="338">
@@ -19518,13 +19518,13 @@
         <v>92</v>
       </c>
       <c r="K338" s="2" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L338" s="2" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M338" s="2" t="n">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="N338" s="4" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>12.5</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="339">
@@ -19589,7 +19589,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>7.03</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="340">
@@ -19646,7 +19646,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>7.03</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="341">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>7.56</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="342">
@@ -19760,7 +19760,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="343">
@@ -19817,7 +19817,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="344">
@@ -19860,13 +19860,13 @@
         <v>83</v>
       </c>
       <c r="K344" s="2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L344" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="345">
@@ -19931,7 +19931,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>7.03</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="346">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="J346" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K346" s="2" t="n">
         <v>286</v>
@@ -19980,7 +19980,7 @@
         <v>67</v>
       </c>
       <c r="M346" s="2" t="n">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="347">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>5.18</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="348">
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>48.48</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="349">
@@ -20145,13 +20145,13 @@
         <v>99</v>
       </c>
       <c r="K349" s="2" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="L349" s="2" t="n">
         <v>178</v>
       </c>
       <c r="M349" s="2" t="n">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="N349" s="4" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="350">
@@ -20216,7 +20216,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="351">
@@ -20273,7 +20273,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="352">
@@ -20330,7 +20330,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>5.54</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="353">
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="354">
@@ -20444,7 +20444,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="355">
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>12.47</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="356">
@@ -20558,7 +20558,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>20.37</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="357">
@@ -20615,7 +20615,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>20.78</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="358">
@@ -20672,7 +20672,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>41.12</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="359">
@@ -20729,7 +20729,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>9.19</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="360">
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>13.23</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="361">
@@ -20843,7 +20843,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>13.23</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="362">
@@ -20900,7 +20900,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="363">
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="364">
@@ -21014,7 +21014,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="365">
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="366">
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>34.66</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="367">
@@ -21185,7 +21185,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>17.79</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="368">
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>34.36</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="369">
@@ -21299,7 +21299,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>14.29</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="370">
@@ -21356,7 +21356,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>9.92</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="371">
@@ -21413,7 +21413,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="372">
@@ -21456,13 +21456,13 @@
         <v>38</v>
       </c>
       <c r="K372" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L372" s="2" t="n">
         <v>38</v>
       </c>
       <c r="M372" s="2" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N372" s="4" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>13.41</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="373">
@@ -21527,7 +21527,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>5.57</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="374">
@@ -21584,7 +21584,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>28.01</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="375">
@@ -21641,7 +21641,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>17.78</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="376">
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>17.78</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="377">
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>23.63</v>
+        <v>23.28</v>
       </c>
     </row>
     <row r="378">
@@ -21812,7 +21812,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>13.57</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="379">
@@ -21869,7 +21869,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>12.83</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="380">
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="381">
@@ -21983,7 +21983,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>6.27</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="382">
@@ -22040,7 +22040,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>7.73</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="383">
@@ -22097,7 +22097,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>14.29</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="384">
@@ -22154,7 +22154,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>14.87</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="385">
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>7.05</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="386">
@@ -22268,7 +22268,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>9.19</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="387">
@@ -22325,7 +22325,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>16.86</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="388">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>13.57</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="389">
@@ -22439,7 +22439,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="390">
@@ -22496,7 +22496,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>34.03</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="391">
@@ -22553,7 +22553,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="392">
@@ -22610,7 +22610,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>15.75</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="393">
@@ -22667,7 +22667,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>18.68</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="394">
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>27.99</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="395">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>8.48</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="396">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>19.03</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="397">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="398">
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="399">
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>6.15</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="400">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="401">
@@ -23119,7 +23119,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="402">
@@ -23160,13 +23160,13 @@
         <v>201</v>
       </c>
       <c r="K402" s="2" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L402" s="2" t="n">
         <v>258</v>
       </c>
       <c r="M402" s="2" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="403">
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="404">
@@ -23270,13 +23270,13 @@
         <v>178</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>266</v>
+        <v>187</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>498</v>
+        <v>419</v>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="405">
@@ -23341,7 +23341,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="406">
@@ -23398,7 +23398,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="407">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="408">
@@ -23512,7 +23512,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="409">
@@ -23555,13 +23555,13 @@
         <v>80</v>
       </c>
       <c r="K409" s="2" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="L409" s="2" t="n">
         <v>168</v>
       </c>
       <c r="M409" s="2" t="n">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="N409" s="4" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="410">
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="411">
@@ -23666,24 +23666,24 @@
         </is>
       </c>
       <c r="J411" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K411" s="2" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L411" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N411" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>226</v>
+      </c>
+      <c r="N411" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="412">
@@ -23726,13 +23726,13 @@
         <v>73</v>
       </c>
       <c r="K412" s="2" t="n">
-        <v>58</v>
+        <v>298</v>
       </c>
       <c r="L412" s="2" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>890</v>
+        <v>1128</v>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="413">
@@ -23783,13 +23783,13 @@
         <v>370</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="L413" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="414">
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="415">
@@ -23911,7 +23911,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="416">
@@ -23954,13 +23954,13 @@
         <v>242</v>
       </c>
       <c r="K416" s="2" t="n">
-        <v>1911</v>
+        <v>1904</v>
       </c>
       <c r="L416" s="2" t="n">
         <v>655</v>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2808</v>
+        <v>2801</v>
       </c>
       <c r="N416" s="4" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="417">
@@ -24014,10 +24014,10 @@
         <v>659</v>
       </c>
       <c r="L417" s="2" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="M417" s="2" t="n">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="418">
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="419">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="420">
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="421">
@@ -24253,7 +24253,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="422">
@@ -24293,7 +24293,7 @@
         </is>
       </c>
       <c r="J422" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K422" s="2" t="n">
         <v>484</v>
@@ -24302,7 +24302,7 @@
         <v>256</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="423">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="424">
@@ -24410,13 +24410,13 @@
         <v>126</v>
       </c>
       <c r="K424" s="2" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="L424" s="2" t="n">
         <v>71</v>
       </c>
       <c r="M424" s="2" t="n">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="N424" s="4" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="425">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="426">
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="J426" s="2" t="n">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="K426" s="2" t="n">
         <v>324</v>
@@ -24530,7 +24530,7 @@
         <v>317</v>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1175</v>
+        <v>1157</v>
       </c>
       <c r="N426" s="4" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="427">
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="428">
@@ -24652,7 +24652,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="429">
@@ -24709,7 +24709,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="430">
@@ -24766,7 +24766,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="431">
@@ -24809,13 +24809,13 @@
         <v>77</v>
       </c>
       <c r="K431" s="2" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L431" s="2" t="n">
         <v>251</v>
       </c>
       <c r="M431" s="2" t="n">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="N431" s="4" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="432">
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="433">
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="434">
@@ -24980,13 +24980,13 @@
         <v>141</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>88</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="N434" s="4" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="435">
@@ -25051,7 +25051,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="436">
@@ -25108,7 +25108,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="437">
@@ -25165,7 +25165,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="438">
@@ -25222,7 +25222,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="439">
@@ -25279,7 +25279,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="440">
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="441">
@@ -25393,7 +25393,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="442">
@@ -25450,7 +25450,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="443">
@@ -25507,7 +25507,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="444">
@@ -25550,13 +25550,13 @@
         <v>167</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="L444" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>403</v>
+        <v>347</v>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="445">
@@ -25621,7 +25621,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="446">
@@ -25678,7 +25678,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="447">
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="448">
@@ -25792,7 +25792,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="449">
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>5.56</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="450">
@@ -25906,7 +25906,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>6.51</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="451">
@@ -25963,7 +25963,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="452">
@@ -26020,7 +26020,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>13.6</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="453">
@@ -26077,7 +26077,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>13.6</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="454">
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="455">
@@ -26177,13 +26177,13 @@
         <v>26</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>17.21</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="456">
@@ -26248,7 +26248,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="457">
@@ -26291,13 +26291,13 @@
         <v>356</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>267</v>
+        <v>167</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>266</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>889</v>
+        <v>789</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="458">
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="459">
@@ -26405,13 +26405,13 @@
         <v>42</v>
       </c>
       <c r="K459" s="2" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L459" s="2" t="n">
         <v>205</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N459" s="4" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="460">
@@ -26462,13 +26462,13 @@
         <v>1</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>235</v>
+        <v>464</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>322</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>558</v>
+        <v>787</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="461">
@@ -26533,7 +26533,7 @@
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="462">
@@ -26576,13 +26576,13 @@
         <v>98</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L462" s="2" t="n">
         <v>85</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="463">
@@ -26633,13 +26633,13 @@
         <v>53</v>
       </c>
       <c r="K463" s="2" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="L463" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M463" s="2" t="n">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="N463" s="4" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="464">
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="465">
@@ -26761,7 +26761,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>7.49</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="466">
@@ -26804,13 +26804,13 @@
         <v>8</v>
       </c>
       <c r="K466" s="2" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="L466" s="2" t="n">
         <v>55</v>
       </c>
       <c r="M466" s="2" t="n">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="N466" s="6" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>7.49</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="467">
@@ -26875,7 +26875,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>10.31</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="468">
@@ -26932,7 +26932,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>10.83</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="469">
@@ -26975,13 +26975,13 @@
         <v>11</v>
       </c>
       <c r="K469" s="2" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="L469" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="N469" s="4" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="470">
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="471">
@@ -27103,7 +27103,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="472">
@@ -27160,7 +27160,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="473">
@@ -27217,7 +27217,7 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>6.42</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="474">
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>7.52</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="475">
@@ -27317,13 +27317,13 @@
         <v>0</v>
       </c>
       <c r="K475" s="2" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L475" s="2" t="n">
         <v>61</v>
       </c>
       <c r="M475" s="2" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="N475" s="6" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="476">
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>8.59</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="477">
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>8.59</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="478">
@@ -27488,13 +27488,13 @@
         <v>1</v>
       </c>
       <c r="K478" s="2" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L478" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M478" s="2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N478" s="6" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="479">
@@ -27559,7 +27559,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>8.07</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="480">
@@ -27616,7 +27616,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>8.07</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="481">
@@ -27673,7 +27673,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>10.3</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="482">
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>30.67</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="483">
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="484">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="485">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="486">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="487">
@@ -28001,13 +28001,13 @@
         <v>51</v>
       </c>
       <c r="K487" s="2" t="n">
-        <v>32</v>
+        <v>314</v>
       </c>
       <c r="L487" s="2" t="n">
         <v>330</v>
       </c>
       <c r="M487" s="2" t="n">
-        <v>413</v>
+        <v>695</v>
       </c>
       <c r="N487" s="4" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         </is>
       </c>
       <c r="O487" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="488">
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="O488" s="2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="489">
@@ -28115,13 +28115,13 @@
         <v>0</v>
       </c>
       <c r="K489" s="2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L489" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M489" s="2" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="N489" s="6" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         </is>
       </c>
       <c r="O489" s="2" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="490">
@@ -28186,7 +28186,7 @@
         </is>
       </c>
       <c r="O490" s="2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="491">
@@ -28243,7 +28243,7 @@
         </is>
       </c>
       <c r="O491" s="2" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="492">
@@ -28300,7 +28300,7 @@
         </is>
       </c>
       <c r="O492" s="2" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="493">
@@ -28357,7 +28357,7 @@
         </is>
       </c>
       <c r="O493" s="2" t="n">
-        <v>4.7</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="494">
@@ -28414,7 +28414,7 @@
         </is>
       </c>
       <c r="O494" s="2" t="n">
-        <v>7.19</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="495">
@@ -28471,7 +28471,7 @@
         </is>
       </c>
       <c r="O495" s="2" t="n">
-        <v>7.19</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="496">
@@ -28511,16 +28511,16 @@
         </is>
       </c>
       <c r="J496" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K496" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L496" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M496" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N496" s="6" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         </is>
       </c>
       <c r="O496" s="2" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="497">
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="O497" s="2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="498">
@@ -28642,7 +28642,7 @@
         </is>
       </c>
       <c r="O498" s="2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="499">
@@ -28699,7 +28699,7 @@
         </is>
       </c>
       <c r="O499" s="2" t="n">
-        <v>8.73</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="500">
@@ -28754,7 +28754,7 @@
         </is>
       </c>
       <c r="O500" s="2" t="n">
-        <v>58.32</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="501">
@@ -28811,7 +28811,7 @@
         </is>
       </c>
       <c r="O501" s="2" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="502">
@@ -28868,7 +28868,7 @@
         </is>
       </c>
       <c r="O502" s="2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -28925,7 +28925,7 @@
         </is>
       </c>
       <c r="O503" s="2" t="n">
-        <v>17.78</v>
+        <v>17.52</v>
       </c>
     </row>
   </sheetData>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>427</v>
@@ -791,7 +791,7 @@
         <v>391</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
         <v>92</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         <v>28</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>154</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
@@ -1170,13 +1170,13 @@
         <v>10</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>13</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
         <v>7</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>12</v>
@@ -2464,7 +2464,7 @@
         <v>185</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>239</v>
@@ -2574,7 +2574,7 @@
         <v>119</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>607</v>
@@ -2684,7 +2684,7 @@
         <v>174</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>99</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>18</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
@@ -2788,13 +2788,13 @@
         <v>142</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>86</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
@@ -2846,10 +2846,10 @@
         <v>52</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>198</v>
@@ -2904,11 +2904,11 @@
         <v>39</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>244</v>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O44" s="2" t="n">
@@ -3173,13 +3173,13 @@
         <v>21</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>62</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -3338,13 +3338,13 @@
         <v>2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
@@ -4823,13 +4823,13 @@
         <v>87</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>170</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
@@ -7776,13 +7776,13 @@
         <v>20</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>149</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
@@ -8118,13 +8118,13 @@
         <v>62</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8232,13 +8232,13 @@
         <v>47</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>228</v>
+        <v>441</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>297</v>
+        <v>507</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
@@ -8346,13 +8346,13 @@
         <v>43</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8805,10 +8805,10 @@
         <v>364</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
@@ -9888,10 +9888,10 @@
         <v>139</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
@@ -10116,10 +10116,10 @@
         <v>68</v>
       </c>
       <c r="L173" s="2" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
         <is>
@@ -10230,10 +10230,10 @@
         <v>22</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
@@ -11367,13 +11367,13 @@
         <v>187</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L195" s="2" t="n">
         <v>149</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
@@ -11766,13 +11766,13 @@
         <v>64</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>377</v>
+        <v>352</v>
       </c>
       <c r="L202" s="2" t="n">
         <v>299</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>740</v>
+        <v>715</v>
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
@@ -11823,13 +11823,13 @@
         <v>167</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="L203" s="2" t="n">
         <v>50</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
@@ -11994,13 +11994,13 @@
         <v>182</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="L206" s="2" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12051,13 +12051,13 @@
         <v>40</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="L207" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
@@ -12165,13 +12165,13 @@
         <v>111</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
@@ -12336,13 +12336,13 @@
         <v>45</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
@@ -12792,13 +12792,13 @@
         <v>0</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L220" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N220" s="5" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>15</v>
@@ -12855,11 +12855,11 @@
         <v>6</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N221" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>21</v>
+      </c>
+      <c r="N221" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O221" s="2" t="n">
@@ -13419,13 +13419,13 @@
         <v>396</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="L231" s="2" t="n">
         <v>691</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1414</v>
+        <v>1404</v>
       </c>
       <c r="N231" s="4" t="inlineStr">
         <is>
@@ -13530,10 +13530,10 @@
         </is>
       </c>
       <c r="J233" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K233" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L233" s="2" t="n">
         <v>0</v>
@@ -13590,13 +13590,13 @@
         <v>1</v>
       </c>
       <c r="K234" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L234" s="2" t="n">
         <v>11</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N234" s="6" t="inlineStr">
         <is>
@@ -14217,13 +14217,13 @@
         <v>0</v>
       </c>
       <c r="K245" s="2" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M245" s="2" t="n">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N245" s="6" t="inlineStr">
         <is>
@@ -14790,10 +14790,10 @@
         <v>0</v>
       </c>
       <c r="L255" s="2" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
@@ -14841,16 +14841,16 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="K256" s="2" t="n">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="L256" s="2" t="n">
         <v>129</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
@@ -15015,13 +15015,13 @@
         <v>82</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L259" s="2" t="n">
         <v>190</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15129,13 +15129,13 @@
         <v>29</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="L261" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15243,13 +15243,13 @@
         <v>71</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L263" s="2" t="n">
         <v>68</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K272" s="2" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
         <v>40</v>
       </c>
       <c r="M272" s="2" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
         <is>
@@ -15813,13 +15813,13 @@
         <v>39</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L273" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M273" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N273" s="4" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>205</v>
       </c>
       <c r="L274" s="2" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="M274" s="2" t="n">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="N274" s="4" t="inlineStr">
         <is>
@@ -16443,10 +16443,10 @@
         <v>328</v>
       </c>
       <c r="L284" s="2" t="n">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="M284" s="2" t="n">
-        <v>437</v>
+        <v>593</v>
       </c>
       <c r="N284" s="4" t="inlineStr">
         <is>
@@ -16956,10 +16956,10 @@
         <v>5</v>
       </c>
       <c r="L293" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M293" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N293" s="4" t="inlineStr">
         <is>
@@ -17409,13 +17409,13 @@
         <v>50</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L301" s="2" t="n">
         <v>77</v>
       </c>
       <c r="M301" s="2" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
@@ -17523,13 +17523,13 @@
         <v>26</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L303" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17697,10 +17697,10 @@
         <v>24</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17979,13 +17979,13 @@
         <v>12</v>
       </c>
       <c r="K311" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L311" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M311" s="2" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N311" s="4" t="inlineStr">
         <is>
@@ -18036,13 +18036,13 @@
         <v>169</v>
       </c>
       <c r="K312" s="2" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L312" s="2" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="M312" s="2" t="n">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="N312" s="4" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         </is>
       </c>
       <c r="J314" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K314" s="2" t="n">
         <v>60</v>
@@ -18156,11 +18156,11 @@
         <v>0</v>
       </c>
       <c r="M314" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="N314" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>69</v>
+      </c>
+      <c r="N314" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O314" s="2" t="n">
@@ -18606,13 +18606,13 @@
         <v>115</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="L322" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M322" s="2" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N322" s="4" t="inlineStr">
         <is>
@@ -18834,13 +18834,13 @@
         <v>44</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="L326" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M326" s="2" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
@@ -19290,13 +19290,13 @@
         <v>7</v>
       </c>
       <c r="K334" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L334" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M334" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N334" s="6" t="inlineStr">
         <is>
@@ -19347,13 +19347,13 @@
         <v>56</v>
       </c>
       <c r="K335" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L335" s="2" t="n">
         <v>83</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19407,10 +19407,10 @@
         <v>87</v>
       </c>
       <c r="L336" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N336" s="4" t="inlineStr">
         <is>
@@ -19518,13 +19518,13 @@
         <v>92</v>
       </c>
       <c r="K338" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L338" s="2" t="n">
         <v>71</v>
       </c>
       <c r="M338" s="2" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N338" s="4" t="inlineStr">
         <is>
@@ -19977,10 +19977,10 @@
         <v>286</v>
       </c>
       <c r="L346" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M346" s="2" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
@@ -20028,20 +20028,20 @@
         </is>
       </c>
       <c r="J347" s="2" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="K347" s="2" t="n">
-        <v>247</v>
+        <v>135</v>
       </c>
       <c r="L347" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M347" s="2" t="n">
-        <v>370</v>
-      </c>
-      <c r="N347" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>356</v>
+      </c>
+      <c r="N347" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O347" s="2" t="n">
@@ -20319,10 +20319,10 @@
         <v>282</v>
       </c>
       <c r="L352" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M352" s="2" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N352" s="4" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         </is>
       </c>
       <c r="J353" s="2" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K353" s="2" t="n">
         <v>183</v>
@@ -20379,7 +20379,7 @@
         <v>26</v>
       </c>
       <c r="M353" s="2" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="N353" s="4" t="inlineStr">
         <is>
@@ -21231,10 +21231,10 @@
         <v>2</v>
       </c>
       <c r="L368" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M368" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N368" s="6" t="inlineStr">
         <is>
@@ -21285,13 +21285,13 @@
         <v>3</v>
       </c>
       <c r="K369" s="2" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L369" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M369" s="2" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N369" s="6" t="inlineStr">
         <is>
@@ -21345,10 +21345,10 @@
         <v>51</v>
       </c>
       <c r="L370" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M370" s="2" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
@@ -21855,13 +21855,13 @@
         <v>0</v>
       </c>
       <c r="K379" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L379" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M379" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N379" s="6" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         </is>
       </c>
       <c r="J381" s="2" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="K381" s="2" t="n">
         <v>151</v>
@@ -21975,7 +21975,7 @@
         <v>94</v>
       </c>
       <c r="M381" s="2" t="n">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
@@ -22764,20 +22764,20 @@
         </is>
       </c>
       <c r="J395" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K395" s="2" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="L395" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M395" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="N395" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>132</v>
+      </c>
+      <c r="N395" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O395" s="2" t="n">
@@ -22881,13 +22881,13 @@
         <v>104</v>
       </c>
       <c r="K397" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L397" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M397" s="2" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="J400" s="2" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K400" s="2" t="n">
         <v>0</v>
@@ -23056,7 +23056,7 @@
         <v>794</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>937</v>
+        <v>927</v>
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
@@ -23270,13 +23270,13 @@
         <v>178</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>419</v>
+        <v>344</v>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
@@ -23894,16 +23894,16 @@
         </is>
       </c>
       <c r="J415" s="2" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>1111</v>
+        <v>1091</v>
       </c>
       <c r="L415" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1309</v>
+        <v>1229</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -23954,13 +23954,13 @@
         <v>242</v>
       </c>
       <c r="K416" s="2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="L416" s="2" t="n">
         <v>655</v>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2801</v>
+        <v>2796</v>
       </c>
       <c r="N416" s="4" t="inlineStr">
         <is>
@@ -24011,13 +24011,13 @@
         <v>179</v>
       </c>
       <c r="K417" s="2" t="n">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="L417" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M417" s="2" t="n">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
@@ -24125,13 +24125,13 @@
         <v>279</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="L419" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         </is>
       </c>
       <c r="J422" s="2" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="K422" s="2" t="n">
         <v>484</v>
@@ -24302,7 +24302,7 @@
         <v>256</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24581,13 +24581,13 @@
         <v>85</v>
       </c>
       <c r="K427" s="2" t="n">
-        <v>642</v>
+        <v>348</v>
       </c>
       <c r="L427" s="2" t="n">
         <v>121</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>848</v>
+        <v>554</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24752,13 +24752,13 @@
         <v>179</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>224</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>587</v>
+        <v>546</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24980,13 +24980,13 @@
         <v>141</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>88</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N434" s="4" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="J438" s="2" t="n">
-        <v>331</v>
+        <v>232</v>
       </c>
       <c r="K438" s="2" t="n">
         <v>341</v>
@@ -25214,7 +25214,7 @@
         <v>81</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>753</v>
+        <v>654</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25550,13 +25550,13 @@
         <v>167</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>85</v>
+        <v>241</v>
       </c>
       <c r="L444" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>347</v>
+        <v>503</v>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -25661,16 +25661,16 @@
         </is>
       </c>
       <c r="J446" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K446" s="2" t="n">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="L446" s="2" t="n">
         <v>38</v>
       </c>
       <c r="M446" s="2" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="N446" s="6" t="inlineStr">
         <is>
@@ -25952,10 +25952,10 @@
         <v>54</v>
       </c>
       <c r="L451" s="2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -26009,10 +26009,10 @@
         <v>1</v>
       </c>
       <c r="L452" s="2" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="M452" s="2" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="N452" s="4" t="inlineStr">
         <is>
@@ -26288,16 +26288,16 @@
         </is>
       </c>
       <c r="J457" s="2" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>266</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26405,13 +26405,13 @@
         <v>42</v>
       </c>
       <c r="K459" s="2" t="n">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="L459" s="2" t="n">
         <v>205</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="N459" s="4" t="inlineStr">
         <is>
@@ -26462,13 +26462,13 @@
         <v>1</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>464</v>
+        <v>359</v>
       </c>
       <c r="L460" s="2" t="n">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>787</v>
+        <v>652</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26519,13 +26519,13 @@
         <v>26</v>
       </c>
       <c r="K461" s="2" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="L461" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="N461" s="4" t="inlineStr">
         <is>
@@ -26975,13 +26975,13 @@
         <v>11</v>
       </c>
       <c r="K469" s="2" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="L469" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="N469" s="4" t="inlineStr">
         <is>
@@ -27029,16 +27029,16 @@
         </is>
       </c>
       <c r="J470" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K470" s="2" t="n">
         <v>117</v>
       </c>
       <c r="L470" s="2" t="n">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="N470" s="6" t="inlineStr">
         <is>
@@ -27089,13 +27089,13 @@
         <v>25</v>
       </c>
       <c r="K471" s="2" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="L471" s="2" t="n">
         <v>77</v>
       </c>
       <c r="M471" s="2" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="N471" s="4" t="inlineStr">
         <is>
@@ -27488,13 +27488,13 @@
         <v>1</v>
       </c>
       <c r="K478" s="2" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="L478" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M478" s="2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N478" s="6" t="inlineStr">
         <is>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -785,13 +785,13 @@
         <v>298</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>391</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
         <v>92</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>116</v>
@@ -1604,7 +1604,7 @@
         <v>86</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>540</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -2348,13 +2348,13 @@
         <v>348</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
@@ -2458,13 +2458,13 @@
         <v>66</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>57</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>174</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2788,13 +2788,13 @@
         <v>142</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>86</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>153</v>
@@ -3069,7 +3069,7 @@
         <v>147</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>466</v>
+        <v>421</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -3338,13 +3338,13 @@
         <v>2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
@@ -3778,13 +3778,13 @@
         <v>40</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
@@ -3833,13 +3833,13 @@
         <v>61</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>53</v>
@@ -4823,13 +4823,13 @@
         <v>87</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>170</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>506</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>11</v>
@@ -5599,7 +5599,7 @@
         <v>103</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N116" s="6" t="inlineStr">
         <is>
@@ -8058,16 +8058,16 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
@@ -8118,13 +8118,13 @@
         <v>62</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>645</v>
+        <v>603</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8403,13 +8403,13 @@
         <v>122</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
@@ -8802,13 +8802,13 @@
         <v>0</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>16</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
@@ -9885,10 +9885,10 @@
         <v>101</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="M169" s="2" t="n">
         <v>319</v>
@@ -10056,13 +10056,13 @@
         <v>256</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>319</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
@@ -10110,16 +10110,16 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>80</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
         <is>
@@ -10626,17 +10626,17 @@
         <v>9</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="N182" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>18</v>
+      </c>
+      <c r="N182" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O182" s="2" t="n">
@@ -11139,13 +11139,13 @@
         <v>52</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L191" s="2" t="n">
         <v>42</v>
       </c>
       <c r="M191" s="2" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="N191" s="4" t="inlineStr">
         <is>
@@ -11253,13 +11253,13 @@
         <v>0</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M193" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N193" s="6" t="inlineStr">
         <is>
@@ -11424,13 +11424,13 @@
         <v>204</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="L196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
@@ -11994,13 +11994,13 @@
         <v>182</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>216</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>30</v>
@@ -12114,7 +12114,7 @@
         <v>76</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="N208" s="4" t="inlineStr">
         <is>
@@ -12165,13 +12165,13 @@
         <v>111</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="L209" s="2" t="n">
         <v>39</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
@@ -12450,13 +12450,13 @@
         <v>120</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L214" s="2" t="n">
         <v>80</v>
       </c>
       <c r="M214" s="2" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N214" s="4" t="inlineStr">
         <is>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L219" s="2" t="n">
         <v>2</v>
@@ -12849,17 +12849,17 @@
         <v>0</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L221" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N221" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>9</v>
+      </c>
+      <c r="N221" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O221" s="2" t="n">
@@ -13020,13 +13020,13 @@
         <v>7</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
@@ -13533,13 +13533,13 @@
         <v>11</v>
       </c>
       <c r="K233" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N233" s="4" t="inlineStr">
         <is>
@@ -13758,20 +13758,20 @@
         </is>
       </c>
       <c r="J237" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K237" s="2" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="L237" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M237" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="N237" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+      <c r="N237" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O237" s="2" t="n">
@@ -13935,10 +13935,10 @@
         <v>17</v>
       </c>
       <c r="L240" s="2" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="M240" s="2" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="N240" s="4" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         </is>
       </c>
       <c r="J247" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K247" s="2" t="n">
         <v>81</v>
@@ -14337,11 +14337,11 @@
         <v>0</v>
       </c>
       <c r="M247" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="N247" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>82</v>
+      </c>
+      <c r="N247" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O247" s="2" t="n">
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="J248" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K248" s="2" t="n">
         <v>0</v>
@@ -14394,7 +14394,7 @@
         <v>0</v>
       </c>
       <c r="M248" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         </is>
       </c>
       <c r="J249" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K249" s="2" t="n">
         <v>192</v>
@@ -14451,7 +14451,7 @@
         <v>182</v>
       </c>
       <c r="M249" s="2" t="n">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="N249" s="4" t="inlineStr">
         <is>
@@ -15015,13 +15015,13 @@
         <v>82</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L259" s="2" t="n">
         <v>190</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15072,13 +15072,13 @@
         <v>139</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L260" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15129,13 +15129,13 @@
         <v>29</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L261" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15300,13 +15300,13 @@
         <v>94</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="L264" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K266" s="2" t="n">
         <v>42</v>
@@ -15420,7 +15420,7 @@
         <v>73</v>
       </c>
       <c r="M266" s="2" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N266" s="4" t="inlineStr">
         <is>
@@ -15873,10 +15873,10 @@
         <v>205</v>
       </c>
       <c r="L274" s="2" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M274" s="2" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N274" s="4" t="inlineStr">
         <is>
@@ -16383,13 +16383,13 @@
         <v>81</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="L283" s="2" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="M283" s="2" t="n">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="N283" s="4" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K284" s="2" t="n">
         <v>328</v>
@@ -16446,7 +16446,7 @@
         <v>238</v>
       </c>
       <c r="M284" s="2" t="n">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="N284" s="4" t="inlineStr">
         <is>
@@ -17349,20 +17349,20 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>246</v>
+        <v>134</v>
       </c>
       <c r="L300" s="2" t="n">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="M300" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="N300" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+      <c r="N300" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O300" s="2" t="n">
@@ -17523,13 +17523,13 @@
         <v>26</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L303" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17583,10 +17583,10 @@
         <v>169</v>
       </c>
       <c r="L304" s="2" t="n">
-        <v>140</v>
+        <v>242</v>
       </c>
       <c r="M304" s="2" t="n">
-        <v>439</v>
+        <v>541</v>
       </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
@@ -17697,10 +17697,10 @@
         <v>24</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17865,13 +17865,13 @@
         <v>38</v>
       </c>
       <c r="K309" s="2" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L309" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M309" s="2" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
@@ -18264,13 +18264,13 @@
         <v>24</v>
       </c>
       <c r="K316" s="2" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="L316" s="2" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="M316" s="2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N316" s="4" t="inlineStr">
         <is>
@@ -18378,10 +18378,10 @@
         <v>11</v>
       </c>
       <c r="K318" s="2" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="L318" s="2" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="M318" s="2" t="n">
         <v>79</v>
@@ -18603,16 +18603,16 @@
         </is>
       </c>
       <c r="J322" s="2" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="L322" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M322" s="2" t="n">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="N322" s="4" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         </is>
       </c>
       <c r="J326" s="2" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K326" s="2" t="n">
         <v>47</v>
@@ -18840,7 +18840,7 @@
         <v>59</v>
       </c>
       <c r="M326" s="2" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
@@ -19002,10 +19002,10 @@
         </is>
       </c>
       <c r="J329" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K329" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L329" s="2" t="n">
         <v>0</v>
@@ -19350,10 +19350,10 @@
         <v>75</v>
       </c>
       <c r="L335" s="2" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19521,10 +19521,10 @@
         <v>2</v>
       </c>
       <c r="L338" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M338" s="2" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N338" s="4" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="J339" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K339" s="2" t="n">
         <v>197</v>
@@ -19581,7 +19581,7 @@
         <v>139</v>
       </c>
       <c r="M339" s="2" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N339" s="4" t="inlineStr">
         <is>
@@ -19860,13 +19860,13 @@
         <v>83</v>
       </c>
       <c r="K344" s="2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L344" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="J346" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K346" s="2" t="n">
         <v>286</v>
@@ -19980,7 +19980,7 @@
         <v>66</v>
       </c>
       <c r="M346" s="2" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
@@ -20031,13 +20031,13 @@
         <v>102</v>
       </c>
       <c r="K347" s="2" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L347" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M347" s="2" t="n">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
@@ -20145,13 +20145,13 @@
         <v>99</v>
       </c>
       <c r="K349" s="2" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L349" s="2" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="M349" s="2" t="n">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="N349" s="4" t="inlineStr">
         <is>
@@ -20373,13 +20373,13 @@
         <v>51</v>
       </c>
       <c r="K353" s="2" t="n">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="L353" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M353" s="2" t="n">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="N353" s="4" t="inlineStr">
         <is>
@@ -20433,10 +20433,10 @@
         <v>11</v>
       </c>
       <c r="L354" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M354" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N354" s="4" t="inlineStr">
         <is>
@@ -20943,10 +20943,10 @@
         <v>0</v>
       </c>
       <c r="K363" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L363" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M363" s="2" t="n">
         <v>5</v>
@@ -21969,13 +21969,13 @@
         <v>93</v>
       </c>
       <c r="K381" s="2" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="L381" s="2" t="n">
         <v>94</v>
       </c>
       <c r="M381" s="2" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
@@ -22824,13 +22824,13 @@
         <v>0</v>
       </c>
       <c r="K396" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L396" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M396" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N396" s="6" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="J397" s="2" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K397" s="2" t="n">
         <v>23</v>
@@ -22887,7 +22887,7 @@
         <v>0</v>
       </c>
       <c r="M397" s="2" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
@@ -23270,13 +23270,13 @@
         <v>178</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
@@ -23384,13 +23384,13 @@
         <v>50</v>
       </c>
       <c r="K406" s="2" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L406" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M406" s="2" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N406" s="4" t="inlineStr">
         <is>
@@ -24011,13 +24011,13 @@
         <v>179</v>
       </c>
       <c r="K417" s="2" t="n">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="L417" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M417" s="2" t="n">
-        <v>914</v>
+        <v>884</v>
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
@@ -24125,13 +24125,13 @@
         <v>279</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="L419" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1155</v>
+        <v>1147</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24293,16 +24293,16 @@
         </is>
       </c>
       <c r="J422" s="2" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="L422" s="2" t="n">
         <v>256</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>861</v>
+        <v>830</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24410,13 +24410,13 @@
         <v>126</v>
       </c>
       <c r="K424" s="2" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="L424" s="2" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="M424" s="2" t="n">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="N424" s="4" t="inlineStr">
         <is>
@@ -24581,13 +24581,13 @@
         <v>85</v>
       </c>
       <c r="K427" s="2" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="L427" s="2" t="n">
         <v>121</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24752,13 +24752,13 @@
         <v>179</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>224</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24923,13 +24923,13 @@
         <v>225</v>
       </c>
       <c r="K433" s="2" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L433" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M433" s="2" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N433" s="4" t="inlineStr">
         <is>
@@ -24980,13 +24980,13 @@
         <v>141</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>88</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N434" s="4" t="inlineStr">
         <is>
@@ -25322,13 +25322,13 @@
         <v>0</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="L440" s="2" t="n">
         <v>244</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="N440" s="6" t="inlineStr">
         <is>
@@ -25493,13 +25493,13 @@
         <v>5</v>
       </c>
       <c r="K443" s="2" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="L443" s="2" t="n">
         <v>210</v>
       </c>
       <c r="M443" s="2" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="N443" s="6" t="inlineStr">
         <is>
@@ -25550,13 +25550,13 @@
         <v>167</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L444" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -25895,10 +25895,10 @@
         <v>23</v>
       </c>
       <c r="L450" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M450" s="2" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N450" s="6" t="inlineStr">
         <is>
@@ -25952,10 +25952,10 @@
         <v>54</v>
       </c>
       <c r="L451" s="2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -26120,13 +26120,13 @@
         <v>4</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L454" s="2" t="n">
         <v>260</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26177,13 +26177,13 @@
         <v>26</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26234,10 +26234,10 @@
         <v>0</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="M456" s="2" t="n">
         <v>167</v>
@@ -26291,13 +26291,13 @@
         <v>352</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>266</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26405,13 +26405,13 @@
         <v>42</v>
       </c>
       <c r="K459" s="2" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L459" s="2" t="n">
         <v>205</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N459" s="4" t="inlineStr">
         <is>
@@ -26462,13 +26462,13 @@
         <v>1</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>292</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>652</v>
+        <v>632</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26576,13 +26576,13 @@
         <v>98</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="L462" s="2" t="n">
         <v>85</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
@@ -26975,13 +26975,13 @@
         <v>11</v>
       </c>
       <c r="K469" s="2" t="n">
-        <v>69</v>
+        <v>212</v>
       </c>
       <c r="L469" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="N469" s="4" t="inlineStr">
         <is>
@@ -28058,13 +28058,13 @@
         <v>0</v>
       </c>
       <c r="K488" s="2" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="L488" s="2" t="n">
         <v>323</v>
       </c>
       <c r="M488" s="2" t="n">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="N488" s="6" t="inlineStr">
         <is>
@@ -28115,13 +28115,13 @@
         <v>0</v>
       </c>
       <c r="K489" s="2" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L489" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M489" s="2" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="N489" s="6" t="inlineStr">
         <is>
@@ -28172,13 +28172,13 @@
         <v>3</v>
       </c>
       <c r="K490" s="2" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L490" s="2" t="n">
         <v>166</v>
       </c>
       <c r="M490" s="2" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N490" s="6" t="inlineStr">
         <is>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -1545,13 +1545,13 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2462</v>
+        <v>2451</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         <v>92</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>86</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         <v>319</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>335</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         <v>318</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>944</v>
+        <v>924</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>298</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1560</v>
+        <v>1540</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         <v>79</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
@@ -2678,13 +2678,13 @@
         <v>57</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>174</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2733,13 +2733,13 @@
         <v>99</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>18</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
@@ -3448,13 +3448,13 @@
         <v>73</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
@@ -3561,10 +3561,10 @@
         <v>78</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
@@ -3668,13 +3668,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
@@ -3778,13 +3778,13 @@
         <v>40</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
@@ -4548,13 +4548,13 @@
         <v>42</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -4603,13 +4603,13 @@
         <v>85</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
@@ -4878,13 +4878,13 @@
         <v>80</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>64</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
@@ -4988,13 +4988,13 @@
         <v>3</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>41</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
@@ -5813,13 +5813,13 @@
         <v>45</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>5</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
@@ -6418,13 +6418,13 @@
         <v>167</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>196</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
         <v>45</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
@@ -8061,13 +8061,13 @@
         <v>23</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
@@ -8232,13 +8232,13 @@
         <v>47</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>19</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
@@ -8346,13 +8346,13 @@
         <v>43</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8802,13 +8802,13 @@
         <v>0</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
@@ -10002,10 +10002,10 @@
         <v>68</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
@@ -10056,13 +10056,13 @@
         <v>256</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>319</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="N172" s="4" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>66</v>
@@ -10119,7 +10119,7 @@
         <v>80</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="N173" s="4" t="inlineStr">
         <is>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L178" s="2" t="n">
         <v>128</v>
@@ -11085,10 +11085,10 @@
         <v>66</v>
       </c>
       <c r="L190" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N190" s="4" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>36</v>
@@ -11430,7 +11430,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
@@ -11763,16 +11763,16 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K202" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="L202" s="2" t="n">
         <v>352</v>
       </c>
-      <c r="L202" s="2" t="n">
-        <v>299</v>
-      </c>
       <c r="M202" s="2" t="n">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>58</v>
@@ -11829,7 +11829,7 @@
         <v>50</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
@@ -12168,10 +12168,10 @@
         <v>88</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
@@ -12564,13 +12564,13 @@
         <v>6</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M216" s="2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
@@ -13134,13 +13134,13 @@
         <v>0</v>
       </c>
       <c r="K226" s="2" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M226" s="2" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N226" s="6" t="inlineStr">
         <is>
@@ -13419,13 +13419,13 @@
         <v>396</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L231" s="2" t="n">
         <v>691</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="N231" s="4" t="inlineStr">
         <is>
@@ -13704,13 +13704,13 @@
         <v>139</v>
       </c>
       <c r="K236" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L236" s="2" t="n">
         <v>244</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N236" s="4" t="inlineStr">
         <is>
@@ -13935,10 +13935,10 @@
         <v>17</v>
       </c>
       <c r="L240" s="2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="M240" s="2" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="N240" s="4" t="inlineStr">
         <is>
@@ -14163,10 +14163,10 @@
         <v>13</v>
       </c>
       <c r="L244" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M244" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N244" s="4" t="inlineStr">
         <is>
@@ -14844,13 +14844,13 @@
         <v>179</v>
       </c>
       <c r="K256" s="2" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="L256" s="2" t="n">
         <v>129</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
@@ -14901,13 +14901,13 @@
         <v>0</v>
       </c>
       <c r="K257" s="2" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="L257" s="2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="N257" s="6" t="inlineStr">
         <is>
@@ -15075,10 +15075,10 @@
         <v>193</v>
       </c>
       <c r="L260" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15129,13 +15129,13 @@
         <v>29</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L261" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15303,10 +15303,10 @@
         <v>46</v>
       </c>
       <c r="L264" s="2" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
@@ -15357,13 +15357,13 @@
         <v>29</v>
       </c>
       <c r="K265" s="2" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L265" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M265" s="2" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N265" s="4" t="inlineStr">
         <is>
@@ -15474,10 +15474,10 @@
         <v>13</v>
       </c>
       <c r="L267" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M267" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N267" s="4" t="inlineStr">
         <is>
@@ -15585,13 +15585,13 @@
         <v>13</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L269" s="2" t="n">
         <v>40</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
         <is>
@@ -15642,13 +15642,13 @@
         <v>55</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L270" s="2" t="n">
         <v>74</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
@@ -15870,13 +15870,13 @@
         <v>39</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="L274" s="2" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M274" s="2" t="n">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="N274" s="4" t="inlineStr">
         <is>
@@ -15930,10 +15930,10 @@
         <v>59</v>
       </c>
       <c r="L275" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M275" s="2" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N275" s="4" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K291" s="2" t="n">
         <v>65</v>
@@ -16845,7 +16845,7 @@
         <v>54</v>
       </c>
       <c r="M291" s="2" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
@@ -17010,13 +17010,13 @@
         <v>159</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>342</v>
+        <v>302</v>
       </c>
       <c r="L294" s="2" t="n">
         <v>105</v>
       </c>
       <c r="M294" s="2" t="n">
-        <v>606</v>
+        <v>566</v>
       </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
@@ -17409,13 +17409,13 @@
         <v>50</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L301" s="2" t="n">
         <v>77</v>
       </c>
       <c r="M301" s="2" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
@@ -17523,13 +17523,13 @@
         <v>26</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L303" s="2" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         </is>
       </c>
       <c r="J310" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K310" s="2" t="n">
         <v>54</v>
@@ -17928,7 +17928,7 @@
         <v>6</v>
       </c>
       <c r="M310" s="2" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
@@ -18435,13 +18435,13 @@
         <v>76</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L319" s="2" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N319" s="4" t="inlineStr">
         <is>
@@ -19404,10 +19404,10 @@
         <v>22</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="L336" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="M336" s="2" t="n">
         <v>116</v>
@@ -19749,10 +19749,10 @@
         <v>92</v>
       </c>
       <c r="L342" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M342" s="2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
@@ -20145,13 +20145,13 @@
         <v>99</v>
       </c>
       <c r="K349" s="2" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="L349" s="2" t="n">
         <v>168</v>
       </c>
       <c r="M349" s="2" t="n">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="N349" s="4" t="inlineStr">
         <is>
@@ -21057,17 +21057,17 @@
         <v>0</v>
       </c>
       <c r="K365" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L365" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M365" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N365" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>19</v>
+      </c>
+      <c r="N365" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O365" s="2" t="n">
@@ -21570,13 +21570,13 @@
         <v>0</v>
       </c>
       <c r="K374" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L374" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M374" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N374" s="6" t="inlineStr">
         <is>
@@ -21966,16 +21966,16 @@
         </is>
       </c>
       <c r="J381" s="2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K381" s="2" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L381" s="2" t="n">
         <v>94</v>
       </c>
       <c r="M381" s="2" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
@@ -22254,10 +22254,10 @@
         <v>74</v>
       </c>
       <c r="K386" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L386" s="2" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M386" s="2" t="n">
         <v>118</v>
@@ -22938,13 +22938,13 @@
         <v>0</v>
       </c>
       <c r="K398" s="2" t="n">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="L398" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M398" s="2" t="n">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="J400" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K400" s="2" t="n">
         <v>0</v>
@@ -23056,7 +23056,7 @@
         <v>794</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
@@ -23105,13 +23105,13 @@
         <v>0</v>
       </c>
       <c r="K401" s="2" t="n">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="L401" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M401" s="2" t="n">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="N401" s="6" t="inlineStr">
         <is>
@@ -23270,13 +23270,13 @@
         <v>178</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>98</v>
+        <v>311</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>330</v>
+        <v>543</v>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
@@ -23555,13 +23555,13 @@
         <v>80</v>
       </c>
       <c r="K409" s="2" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="L409" s="2" t="n">
         <v>168</v>
       </c>
       <c r="M409" s="2" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="N409" s="4" t="inlineStr">
         <is>
@@ -23615,10 +23615,10 @@
         <v>682</v>
       </c>
       <c r="L410" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M410" s="2" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="N410" s="4" t="inlineStr">
         <is>
@@ -23669,13 +23669,13 @@
         <v>6</v>
       </c>
       <c r="K411" s="2" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L411" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N411" s="6" t="inlineStr">
         <is>
@@ -23897,13 +23897,13 @@
         <v>138</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>1091</v>
+        <v>1071</v>
       </c>
       <c r="L415" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1229</v>
+        <v>1209</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -23954,13 +23954,13 @@
         <v>242</v>
       </c>
       <c r="K416" s="2" t="n">
-        <v>1899</v>
+        <v>1880</v>
       </c>
       <c r="L416" s="2" t="n">
-        <v>655</v>
+        <v>605</v>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2796</v>
+        <v>2727</v>
       </c>
       <c r="N416" s="4" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         <v>624</v>
       </c>
       <c r="L417" s="2" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="M417" s="2" t="n">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
@@ -24125,13 +24125,13 @@
         <v>279</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>861</v>
+        <v>580</v>
       </c>
       <c r="L419" s="2" t="n">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1147</v>
+        <v>1096</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24293,16 +24293,16 @@
         </is>
       </c>
       <c r="J422" s="2" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="L422" s="2" t="n">
         <v>256</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>830</v>
+        <v>796</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24752,13 +24752,13 @@
         <v>179</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>224</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24923,13 +24923,13 @@
         <v>225</v>
       </c>
       <c r="K433" s="2" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L433" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M433" s="2" t="n">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="N433" s="4" t="inlineStr">
         <is>
@@ -24983,10 +24983,10 @@
         <v>12</v>
       </c>
       <c r="L434" s="2" t="n">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="N434" s="4" t="inlineStr">
         <is>
@@ -25094,13 +25094,13 @@
         <v>60</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="L436" s="2" t="n">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
@@ -25322,13 +25322,13 @@
         <v>0</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="L440" s="2" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="N440" s="6" t="inlineStr">
         <is>
@@ -25439,10 +25439,10 @@
         <v>219</v>
       </c>
       <c r="L442" s="2" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="N442" s="4" t="inlineStr">
         <is>
@@ -25550,13 +25550,13 @@
         <v>167</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L444" s="2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -26120,13 +26120,13 @@
         <v>4</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L454" s="2" t="n">
         <v>260</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26177,13 +26177,13 @@
         <v>26</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26234,13 +26234,13 @@
         <v>0</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="N456" s="6" t="inlineStr">
         <is>
@@ -26291,13 +26291,13 @@
         <v>352</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>266</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26348,13 +26348,13 @@
         <v>275</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="L458" s="2" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="N458" s="4" t="inlineStr">
         <is>
@@ -26459,20 +26459,20 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>1</v>
+        <v>616</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>339</v>
+        <v>43</v>
       </c>
       <c r="L460" s="2" t="n">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>632</v>
-      </c>
-      <c r="N460" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>787</v>
+      </c>
+      <c r="N460" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O460" s="2" t="n">
@@ -26519,13 +26519,13 @@
         <v>26</v>
       </c>
       <c r="K461" s="2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L461" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="N461" s="4" t="inlineStr">
         <is>
@@ -26576,13 +26576,13 @@
         <v>98</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L462" s="2" t="n">
         <v>85</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
@@ -27032,13 +27032,13 @@
         <v>8</v>
       </c>
       <c r="K470" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L470" s="2" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="N470" s="6" t="inlineStr">
         <is>
@@ -27203,13 +27203,13 @@
         <v>11</v>
       </c>
       <c r="K473" s="2" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="L473" s="2" t="n">
         <v>91</v>
       </c>
       <c r="M473" s="2" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N473" s="4" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         </is>
       </c>
       <c r="J474" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K474" s="2" t="n">
         <v>138</v>
@@ -27266,7 +27266,7 @@
         <v>81</v>
       </c>
       <c r="M474" s="2" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N474" s="4" t="inlineStr">
         <is>
@@ -27488,13 +27488,13 @@
         <v>1</v>
       </c>
       <c r="K478" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L478" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M478" s="2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N478" s="6" t="inlineStr">
         <is>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.65€/kg)</t>
+          <t>€/m (6.5€/kg)</t>
         </is>
       </c>
     </row>
@@ -618,13 +618,13 @@
         <v>45</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.25</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>80.8</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="5">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -840,13 +840,13 @@
         <v>107</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>66</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="7">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.21</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="8">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>11.22</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="9">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.15</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="10">
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>28.83</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="11">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="12">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>45.05</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="13">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>21</v>
@@ -1231,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>36.34</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="14">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="15">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="17">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="18">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="19">
@@ -1548,10 +1548,10 @@
         <v>150</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2301</v>
+        <v>1501</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2451</v>
+        <v>1651</v>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="20">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="21">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>5.64</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="22">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>8.81</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>12.69</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="24">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>17.28</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="25">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>22.56</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="26">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>35.26</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="27">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>50.77</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="28">
@@ -2022,13 +2022,13 @@
         <v>319</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>335</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1191</v>
+        <v>1161</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="29">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>6.82</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="30">
@@ -2128,13 +2128,13 @@
         <v>213</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>77</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -2183,13 +2183,13 @@
         <v>318</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>924</v>
+        <v>914</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>298</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="32">
@@ -2238,13 +2238,13 @@
         <v>168</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>150</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="33">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="34">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="35">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="36">
@@ -2458,13 +2458,13 @@
         <v>66</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>181</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="37">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="38">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>5.41</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="39">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>10.77</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="40">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>584</v>
@@ -2684,7 +2684,7 @@
         <v>174</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="41">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>5.76</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="42">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>7.21</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="43">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>10.77</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="44">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="45">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="46">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="47">
@@ -3066,10 +3066,10 @@
         <v>153</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="48">
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>7.18</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="49">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>9.01</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="50">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>13.47</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="51">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>17.96</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="52">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>10.77</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="53">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>12.93</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="54">
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>16.15</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="55">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>21.54</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="56">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>12.56</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="57">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.52</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="58">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>11.52</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="59">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>14.41</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="60">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>21.63</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="61">
@@ -3833,13 +3833,13 @@
         <v>61</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>28.73</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="62">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>14.36</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="63">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>18.01</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="64">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>21.13</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="65">
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>21.51</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="66">
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>25.86</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="67">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>35.01</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>26.92</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="69">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>8.98</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>20.2</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="71">
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>35.91</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="72">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>14.36</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="73">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="74">
@@ -4548,13 +4548,13 @@
         <v>42</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="75">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>8.08</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="76">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="77">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="78">
@@ -4768,13 +4768,13 @@
         <v>117</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="79">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="80">
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="81">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="82">
@@ -4988,13 +4988,13 @@
         <v>3</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>201</v>
+        <v>31</v>
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="83">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>35.91</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="84">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>32.32</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="85">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>43.09</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="86">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>53.86</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="87">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>26.43</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="88">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="89">
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>40.4</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="90">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>25.14</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="91">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>7.18</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="92">
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="93">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="94">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="95">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>21.4</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="96">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>21.4</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="97">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="98">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>8.08</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="99">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>6.28</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="100">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="101">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="102">
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="103">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>8.08</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="104">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>16.16</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="105">
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>17.24</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="106">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="107">
@@ -6363,13 +6363,13 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>12.93</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="108">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="109">
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="110">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="111">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>28.73</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="112">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="113">
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>13.47</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="114">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="115">
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="116">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>11.03</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="117">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="118">
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>16.12</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="119">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>25.76</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="120">
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>59.68</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="121">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>5.08</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="122">
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>7.24</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="123">
@@ -7263,13 +7263,13 @@
         <v>7</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>133</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="124">
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="125">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>23.05</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="126">
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.16</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="127">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>118</v>
@@ -7611,7 +7611,7 @@
         <v>82</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="130">
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>6.12</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="131">
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>15.94</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="132">
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="133">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="134">
@@ -7904,7 +7904,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>10.19</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="136">
@@ -8004,13 +8004,13 @@
         <v>104</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>123</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="137">
@@ -8061,13 +8061,13 @@
         <v>23</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="139">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="140">
@@ -8232,13 +8232,13 @@
         <v>47</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="141">
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="142">
@@ -8346,13 +8346,13 @@
         <v>43</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="143">
@@ -8403,13 +8403,13 @@
         <v>122</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>12.28</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="144">
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>14.43</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="145">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>21.83</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="146">
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>34.11</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="147">
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="148">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="149">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="150">
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>5.23</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="151">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>5.83</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="153">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>41.43</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="154">
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>41.43</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="155">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>11.21</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="156">
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>20.9</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="157">
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>10.61</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="158">
@@ -9272,7 +9272,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="159">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="160">
@@ -9386,7 +9386,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>10.49</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="161">
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="162">
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="163">
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>10.73</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="164">
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>10.73</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="165">
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>4.62</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="166">
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>39.31</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="167">
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>43.24</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="168">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="169">
@@ -9885,13 +9885,13 @@
         <v>101</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>6.92</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="170">
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="172">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="173">
@@ -10127,7 +10127,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="174">
@@ -10184,7 +10184,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>15.51</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="175">
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>13.02</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="176">
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="177">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="178">
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>46</v>
@@ -10404,7 +10404,7 @@
         <v>128</v>
       </c>
       <c r="M178" s="2" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="N178" s="6" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>4.95</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="179">
@@ -10469,7 +10469,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>9</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="180">
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="181">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.02</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="182">
@@ -10640,7 +10640,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>6.26</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="183">
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="184">
@@ -10754,7 +10754,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="185">
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="186">
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="187">
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="188">
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="189">
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="190">
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>4.24</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="191">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>10.07</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="192">
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="193">
@@ -11267,7 +11267,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="194">
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="195">
@@ -11381,7 +11381,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="196">
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="199">
@@ -11609,7 +11609,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="200">
@@ -11666,7 +11666,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="201">
@@ -11723,7 +11723,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -11780,7 +11780,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="203">
@@ -11837,7 +11837,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="204">
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="205">
@@ -11951,7 +11951,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>5.4</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="206">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>285</v>
@@ -12000,7 +12000,7 @@
         <v>216</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="207">
@@ -12051,13 +12051,13 @@
         <v>40</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="208">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>4.58</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="209">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>5.31</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="210">
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="211">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="212">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>7.95</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="213">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>12.69</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="214">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>12.69</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="215">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>12.68</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="216">
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>15.51</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="217">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>21.23</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="218">
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>50.77</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="219">
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>50.77</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="220">
@@ -12806,7 +12806,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>25.74</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="221">
@@ -12863,7 +12863,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>18.1</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="222">
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>29.61</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="223">
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>26.79</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="224">
@@ -13020,13 +13020,13 @@
         <v>7</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M224" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>26.79</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="225">
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="226">
@@ -13148,7 +13148,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="227">
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="228">
@@ -13262,7 +13262,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>13.07</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="229">
@@ -13319,7 +13319,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>23.97</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="230">
@@ -13376,7 +13376,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>65.66</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -13419,13 +13419,13 @@
         <v>396</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="L231" s="2" t="n">
         <v>691</v>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="N231" s="4" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="232">
@@ -13476,13 +13476,13 @@
         <v>16</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="L232" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="N232" s="4" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>6.54</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="233">
@@ -13547,7 +13547,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>23.34</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="234">
@@ -13604,7 +13604,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>11.1</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="235">
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>8.15</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="236">
@@ -13718,7 +13718,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>5.41</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="237">
@@ -13775,7 +13775,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>10.92</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="238">
@@ -13832,7 +13832,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="239">
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="240">
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="241">
@@ -14003,7 +14003,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>19.8</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="242">
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="243">
@@ -14117,7 +14117,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>4.92</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="244">
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="J244" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K244" s="2" t="n">
         <v>13</v>
@@ -14166,7 +14166,7 @@
         <v>12</v>
       </c>
       <c r="M244" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N244" s="4" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>5.43</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="245">
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="246">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>69.53</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>14.88</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="248">
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>41.76</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="249">
@@ -14459,7 +14459,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="250">
@@ -14516,7 +14516,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="251">
@@ -14559,13 +14559,13 @@
         <v>0</v>
       </c>
       <c r="K251" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L251" s="2" t="n">
         <v>38</v>
       </c>
       <c r="M251" s="2" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N251" s="6" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>7.63</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="252">
@@ -14630,7 +14630,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>5.98</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="253">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>4.08</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="254">
@@ -14744,7 +14744,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>21.73</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="255">
@@ -14801,7 +14801,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="256">
@@ -14858,7 +14858,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="257">
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="258">
@@ -14972,7 +14972,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="259">
@@ -15015,13 +15015,13 @@
         <v>82</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L259" s="2" t="n">
         <v>190</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>5.82</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="260">
@@ -15072,13 +15072,13 @@
         <v>139</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L260" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="261">
@@ -15129,13 +15129,13 @@
         <v>29</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L261" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="262">
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>6.76</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="263">
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>10.34</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="264">
@@ -15314,7 +15314,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="265">
@@ -15357,13 +15357,13 @@
         <v>29</v>
       </c>
       <c r="K265" s="2" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L265" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M265" s="2" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N265" s="4" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>13.21</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="266">
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>12.34</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="267">
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>16.09</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="268">
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>16.09</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="269">
@@ -15599,7 +15599,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>18.95</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="270">
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>21.83</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="271">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>41.37</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="272">
@@ -15753,7 +15753,7 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K272" s="2" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
         <v>40</v>
       </c>
       <c r="M272" s="2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>27.48</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="273">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>16.66</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="274">
@@ -15867,7 +15867,7 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K274" s="2" t="n">
         <v>199</v>
@@ -15876,15 +15876,15 @@
         <v>136</v>
       </c>
       <c r="M274" s="2" t="n">
-        <v>374</v>
-      </c>
-      <c r="N274" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>335</v>
+      </c>
+      <c r="N274" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="275">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>6.18</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="276">
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="277">
@@ -16055,7 +16055,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="278">
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>26.56</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="279">
@@ -16169,7 +16169,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>26.56</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="280">
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>41.3</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="281">
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>4.97</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="282">
@@ -16340,7 +16340,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="283">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="284">
@@ -16454,7 +16454,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>7.97</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="285">
@@ -16511,7 +16511,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="286">
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>10.09</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="287">
@@ -16611,13 +16611,13 @@
         <v>5</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="L287" s="2" t="n">
         <v>70</v>
       </c>
       <c r="M287" s="2" t="n">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="N287" s="6" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>5.68</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="288">
@@ -16682,7 +16682,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>12.27</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="289">
@@ -16739,7 +16739,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>13.07</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="290">
@@ -16796,7 +16796,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>40.14</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="291">
@@ -16853,7 +16853,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>10.13</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="292">
@@ -16910,7 +16910,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>27.5</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="293">
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>27.5</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="294">
@@ -17024,7 +17024,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="295">
@@ -17081,7 +17081,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="296">
@@ -17138,7 +17138,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>21.34</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="297">
@@ -17195,7 +17195,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="298">
@@ -17252,7 +17252,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="299">
@@ -17309,7 +17309,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>68</v>
       </c>
     </row>
     <row r="300">
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>10.33</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="301">
@@ -17409,13 +17409,13 @@
         <v>50</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L301" s="2" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="M301" s="2" t="n">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>4.02</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="302">
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>4.02</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="303">
@@ -17523,13 +17523,13 @@
         <v>26</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L303" s="2" t="n">
         <v>23</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="304">
@@ -17594,7 +17594,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>7.97</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="305">
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="306">
@@ -17694,13 +17694,13 @@
         <v>54</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>10.13</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="307">
@@ -17765,7 +17765,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>10.13</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="308">
@@ -17822,7 +17822,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>10.16</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="309">
@@ -17879,7 +17879,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>16.08</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="310">
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>18.96</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="311">
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>20.4</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="312">
@@ -18050,7 +18050,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="313">
@@ -18107,7 +18107,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="314">
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>40.75</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="315">
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>22.84</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="316">
@@ -18278,7 +18278,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>24.13</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="317">
@@ -18335,7 +18335,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>9.039999999999999</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="318">
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>17.67</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="319">
@@ -18435,13 +18435,13 @@
         <v>76</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L319" s="2" t="n">
         <v>58</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N319" s="4" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>9.77</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="320">
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>18.96</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="321">
@@ -18563,7 +18563,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>30.52</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="322">
@@ -18620,7 +18620,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="324">
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="325">
@@ -18791,7 +18791,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="326">
@@ -18834,13 +18834,13 @@
         <v>28</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L326" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M326" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>10.49</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="327">
@@ -18905,7 +18905,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>10.49</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="328">
@@ -18962,7 +18962,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>20.88</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="329">
@@ -19019,7 +19019,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>15.81</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="330">
@@ -19076,7 +19076,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>14.11</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="331">
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>12.64</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="332">
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>24.7</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="333">
@@ -19247,7 +19247,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="334">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>20.85</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="335">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>5.82</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="336">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>16.59</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="337">
@@ -19458,7 +19458,7 @@
         </is>
       </c>
       <c r="J337" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K337" s="2" t="n">
         <v>15</v>
@@ -19467,7 +19467,7 @@
         <v>32</v>
       </c>
       <c r="M337" s="2" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N337" s="4" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>25.21</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="338">
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>12.32</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="339">
@@ -19589,7 +19589,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>6.93</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="340">
@@ -19646,7 +19646,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>6.93</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="341">
@@ -19703,7 +19703,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>7.45</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="342">
@@ -19760,7 +19760,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>7.64</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="343">
@@ -19817,7 +19817,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>7.64</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="344">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="J344" s="2" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="K344" s="2" t="n">
         <v>70</v>
@@ -19866,15 +19866,15 @@
         <v>23</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="N344" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>95</v>
+      </c>
+      <c r="N344" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="345">
@@ -19931,7 +19931,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>6.92</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="346">
@@ -19974,13 +19974,13 @@
         <v>60</v>
       </c>
       <c r="K346" s="2" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L346" s="2" t="n">
         <v>66</v>
       </c>
       <c r="M346" s="2" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="347">
@@ -20045,7 +20045,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>5.1</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="348">
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>47.76</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="349">
@@ -20148,10 +20148,10 @@
         <v>246</v>
       </c>
       <c r="L349" s="2" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M349" s="2" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N349" s="4" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="350">
@@ -20216,7 +20216,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>6.9</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="351">
@@ -20273,7 +20273,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>12.28</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="352">
@@ -20316,13 +20316,13 @@
         <v>220</v>
       </c>
       <c r="K352" s="2" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L352" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M352" s="2" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="N352" s="4" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>5.46</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="353">
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -20444,7 +20444,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>12.28</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="355">
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>12.28</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="356">
@@ -20558,7 +20558,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>20.07</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="357">
@@ -20615,7 +20615,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>20.47</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="358">
@@ -20672,7 +20672,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>40.51</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="359">
@@ -20715,13 +20715,13 @@
         <v>27</v>
       </c>
       <c r="K359" s="2" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L359" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M359" s="2" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N359" s="4" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="360">
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>13.03</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="361">
@@ -20843,7 +20843,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>13.03</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="362">
@@ -20900,7 +20900,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>34.15</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="363">
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>34.15</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="364">
@@ -21014,7 +21014,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>34.15</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="365">
@@ -21057,13 +21057,13 @@
         <v>0</v>
       </c>
       <c r="K365" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L365" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M365" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N365" s="6" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>34.15</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="366">
@@ -21128,7 +21128,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>34.15</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="367">
@@ -21185,7 +21185,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>17.52</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="368">
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>33.85</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="369">
@@ -21299,7 +21299,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>14.08</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="370">
@@ -21356,7 +21356,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>9.77</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="371">
@@ -21413,7 +21413,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="372">
@@ -21470,7 +21470,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>13.21</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="373">
@@ -21527,7 +21527,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>5.49</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="374">
@@ -21584,7 +21584,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>27.6</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="375">
@@ -21641,7 +21641,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>17.52</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="376">
@@ -21698,7 +21698,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>17.52</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="377">
@@ -21755,7 +21755,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>23.28</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="378">
@@ -21801,10 +21801,10 @@
         <v>26</v>
       </c>
       <c r="L378" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M378" s="2" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N378" s="4" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>13.37</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="379">
@@ -21869,7 +21869,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>12.64</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="380">
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="381">
@@ -21983,7 +21983,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>6.18</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="382">
@@ -22040,7 +22040,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>7.61</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="383">
@@ -22097,7 +22097,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>14.08</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="384">
@@ -22154,7 +22154,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>14.65</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="385">
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="386">
@@ -22257,10 +22257,10 @@
         <v>0</v>
       </c>
       <c r="L386" s="2" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="M386" s="2" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="N386" s="4" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="387">
@@ -22325,7 +22325,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>16.61</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="388">
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>13.37</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="389">
@@ -22439,7 +22439,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="390">
@@ -22496,7 +22496,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>33.52</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="391">
@@ -22553,7 +22553,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="392">
@@ -22610,7 +22610,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>15.52</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="393">
@@ -22667,7 +22667,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>18.4</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="394">
@@ -22724,7 +22724,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>27.58</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="395">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>8.35</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="396">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>18.75</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="397">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="398">
@@ -22938,13 +22938,13 @@
         <v>0</v>
       </c>
       <c r="K398" s="2" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="L398" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M398" s="2" t="n">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="399">
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>6.06</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="400">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="401">
@@ -23119,7 +23119,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="402">
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="403">
@@ -23229,7 +23229,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="404">
@@ -23270,13 +23270,13 @@
         <v>178</v>
       </c>
       <c r="K404" s="2" t="n">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L404" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M404" s="2" t="n">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="405">
@@ -23341,7 +23341,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="406">
@@ -23398,7 +23398,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="407">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="408">
@@ -23512,7 +23512,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="409">
@@ -23555,13 +23555,13 @@
         <v>80</v>
       </c>
       <c r="K409" s="2" t="n">
-        <v>570</v>
+        <v>512</v>
       </c>
       <c r="L409" s="2" t="n">
         <v>168</v>
       </c>
       <c r="M409" s="2" t="n">
-        <v>818</v>
+        <v>760</v>
       </c>
       <c r="N409" s="4" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="410">
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="411">
@@ -23683,7 +23683,7 @@
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="412">
@@ -23740,7 +23740,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="413">
@@ -23797,7 +23797,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="414">
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="415">
@@ -23911,7 +23911,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="416">
@@ -23968,7 +23968,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="417">
@@ -24011,13 +24011,13 @@
         <v>179</v>
       </c>
       <c r="K417" s="2" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="L417" s="2" t="n">
         <v>61</v>
       </c>
       <c r="M417" s="2" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="418">
@@ -24068,13 +24068,13 @@
         <v>0</v>
       </c>
       <c r="K418" s="2" t="n">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="L418" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="N418" s="6" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="419">
@@ -24125,13 +24125,13 @@
         <v>279</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="L419" s="2" t="n">
         <v>237</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="420">
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="421">
@@ -24253,7 +24253,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="422">
@@ -24299,10 +24299,10 @@
         <v>450</v>
       </c>
       <c r="L422" s="2" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="423">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="424">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="425">
@@ -24467,13 +24467,13 @@
         <v>0</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L425" s="2" t="n">
         <v>109</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N425" s="6" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="426">
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="427">
@@ -24578,16 +24578,16 @@
         </is>
       </c>
       <c r="J427" s="2" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="K427" s="2" t="n">
-        <v>341</v>
+        <v>248</v>
       </c>
       <c r="L427" s="2" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>547</v>
+        <v>510</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="428">
@@ -24652,7 +24652,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="429">
@@ -24709,7 +24709,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="430">
@@ -24752,13 +24752,13 @@
         <v>179</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="L430" s="2" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="431">
@@ -24809,13 +24809,13 @@
         <v>77</v>
       </c>
       <c r="K431" s="2" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="L431" s="2" t="n">
         <v>251</v>
       </c>
       <c r="M431" s="2" t="n">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="N431" s="4" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="432">
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="433">
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="434">
@@ -24994,7 +24994,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>4.47</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="435">
@@ -25051,7 +25051,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="436">
@@ -25094,13 +25094,13 @@
         <v>60</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="L436" s="2" t="n">
         <v>215</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="437">
@@ -25165,7 +25165,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="438">
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="J438" s="2" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K438" s="2" t="n">
         <v>341</v>
@@ -25214,7 +25214,7 @@
         <v>81</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="439">
@@ -25279,7 +25279,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="440">
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="441">
@@ -25393,7 +25393,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="442">
@@ -25436,13 +25436,13 @@
         <v>216</v>
       </c>
       <c r="K442" s="2" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L442" s="2" t="n">
         <v>264</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="N442" s="4" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="443">
@@ -25507,7 +25507,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="444">
@@ -25547,7 +25547,7 @@
         </is>
       </c>
       <c r="J444" s="2" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K444" s="2" t="n">
         <v>230</v>
@@ -25556,7 +25556,7 @@
         <v>85</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="445">
@@ -25621,7 +25621,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="446">
@@ -25678,7 +25678,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="447">
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="448">
@@ -25792,7 +25792,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="449">
@@ -25849,7 +25849,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>5.48</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="450">
@@ -25906,7 +25906,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>6.41</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="451">
@@ -25949,13 +25949,13 @@
         <v>11</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L451" s="2" t="n">
         <v>67</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="452">
@@ -26020,7 +26020,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>13.39</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="453">
@@ -26077,7 +26077,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>13.39</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="454">
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>3.16</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="455">
@@ -26177,13 +26177,13 @@
         <v>26</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>16.95</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="456">
@@ -26248,7 +26248,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="457">
@@ -26291,13 +26291,13 @@
         <v>352</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>266</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="458">
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="459">
@@ -26402,7 +26402,7 @@
         </is>
       </c>
       <c r="J459" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K459" s="2" t="n">
         <v>203</v>
@@ -26411,7 +26411,7 @@
         <v>205</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N459" s="4" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -26459,16 +26459,16 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>616</v>
+        <v>497</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>128</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>787</v>
+        <v>810</v>
       </c>
       <c r="N460" s="4" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="461">
@@ -26516,7 +26516,7 @@
         </is>
       </c>
       <c r="J461" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K461" s="2" t="n">
         <v>190</v>
@@ -26525,15 +26525,15 @@
         <v>24</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="N461" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>214</v>
+      </c>
+      <c r="N461" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="462">
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="463">
@@ -26647,7 +26647,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="464">
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="465">
@@ -26761,7 +26761,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>7.38</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="466">
@@ -26818,7 +26818,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>7.38</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="467">
@@ -26875,7 +26875,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>10.16</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="468">
@@ -26932,7 +26932,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="469">
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>4.54</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="470">
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>6.3</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="471">
@@ -27103,7 +27103,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>3.88</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="472">
@@ -27160,7 +27160,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="473">
@@ -27217,7 +27217,7 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>6.33</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="474">
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>7.41</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="475">
@@ -27331,7 +27331,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="476">
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="477">
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="478">
@@ -27502,7 +27502,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>9</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="479">
@@ -27559,7 +27559,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>7.95</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="480">
@@ -27616,7 +27616,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>7.95</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="481">
@@ -27673,7 +27673,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>10.15</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="482">
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>30.22</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="483">
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="484">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="485">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="486">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="487">
@@ -28015,7 +28015,7 @@
         </is>
       </c>
       <c r="O487" s="2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="488">
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="O488" s="2" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="489">
@@ -28129,7 +28129,7 @@
         </is>
       </c>
       <c r="O489" s="2" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="490">
@@ -28186,7 +28186,7 @@
         </is>
       </c>
       <c r="O490" s="2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="491">
@@ -28243,7 +28243,7 @@
         </is>
       </c>
       <c r="O491" s="2" t="n">
-        <v>4.11</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="492">
@@ -28300,7 +28300,7 @@
         </is>
       </c>
       <c r="O492" s="2" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="493">
@@ -28357,7 +28357,7 @@
         </is>
       </c>
       <c r="O493" s="2" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="494">
@@ -28414,7 +28414,7 @@
         </is>
       </c>
       <c r="O494" s="2" t="n">
-        <v>7.08</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="495">
@@ -28471,7 +28471,7 @@
         </is>
       </c>
       <c r="O495" s="2" t="n">
-        <v>7.08</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="496">
@@ -28514,13 +28514,13 @@
         <v>6</v>
       </c>
       <c r="K496" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L496" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M496" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N496" s="6" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         </is>
       </c>
       <c r="O496" s="2" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="497">
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="O497" s="2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="498">
@@ -28628,13 +28628,13 @@
         <v>0</v>
       </c>
       <c r="K498" s="2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L498" s="2" t="n">
         <v>67</v>
       </c>
       <c r="M498" s="2" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N498" s="6" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         </is>
       </c>
       <c r="O498" s="2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="499">
@@ -28699,7 +28699,7 @@
         </is>
       </c>
       <c r="O499" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="500">
@@ -28754,7 +28754,7 @@
         </is>
       </c>
       <c r="O500" s="2" t="n">
-        <v>57.46</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="501">
@@ -28811,7 +28811,7 @@
         </is>
       </c>
       <c r="O501" s="2" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="502">
@@ -28868,7 +28868,7 @@
         </is>
       </c>
       <c r="O502" s="2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="503">
@@ -28925,7 +28925,7 @@
         </is>
       </c>
       <c r="O503" s="2" t="n">
-        <v>17.52</v>
+        <v>17.12</v>
       </c>
     </row>
   </sheetData>
